--- a/examples/gerados/RSO-Demonstracao.xlsx
+++ b/examples/gerados/RSO-Demonstracao.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 RSO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 RSO e fotos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Fotos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Fotos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Dados" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="01 RSO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02 RSO e fotos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03 Fotos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="_Dados" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'01 RSO'!$A$1:$S$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02 RSO e fotos'!$A$1:$I$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'03 Fotos'!$A$1:$F$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'04 Fotos'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02 RSO e fotos'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03 Fotos'!$A$1:$D$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.##%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,12 +91,6 @@
     <font>
       <name val="Tw Cen MT"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <b val="1"/>
       <color rgb="00548235"/>
       <sz val="9"/>
     </font>
@@ -112,14 +104,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="9.9"/>
     </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <b val="1"/>
-      <color rgb="00548235"/>
-      <sz val="8.5"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -144,11 +130,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00A9D18E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDF3E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -250,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -336,30 +317,16 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,7 +406,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>16</col>
@@ -454,13 +421,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -479,13 +446,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -504,13 +471,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -529,13 +496,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -544,13 +511,13 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>2</col>
       <colOff>155666</colOff>
       <row>14</row>
-      <rowOff>50800</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="2439489" cy="1828800"/>
     <pic>
@@ -559,23 +526,23 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
-      <colOff>385352</colOff>
+      <col>4</col>
+      <colOff>2326992</colOff>
       <row>14</row>
-      <rowOff>50800</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="2437315" cy="1828800"/>
     <pic>
@@ -584,20 +551,70 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>2</col>
+      <colOff>155666</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2439489" cy="1828800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>2326992</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2437315" cy="1828800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>181629</colOff>
       <row>18</row>
       <rowOff>0</rowOff>
@@ -605,17 +622,17 @@
     <ext cx="1262342" cy="546100"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -624,13 +641,13 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>384266</colOff>
       <row>4</row>
-      <rowOff>50800</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="2439489" cy="1828800"/>
     <pic>
@@ -639,23 +656,23 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>385352</colOff>
+      <col>1</col>
+      <colOff>3745772</colOff>
       <row>4</row>
-      <rowOff>50800</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="2437315" cy="1828800"/>
     <pic>
@@ -664,13 +681,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -680,7 +697,7 @@
       <col>1</col>
       <colOff>384266</colOff>
       <row>6</row>
-      <rowOff>101600</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="2439489" cy="1828800"/>
     <pic>
@@ -689,23 +706,23 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>385352</colOff>
+      <col>1</col>
+      <colOff>3745772</colOff>
       <row>6</row>
-      <rowOff>101600</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="2437315" cy="1828800"/>
     <pic>
@@ -714,202 +731,22 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>384266</colOff>
-      <row>10</row>
-      <rowOff>50800</rowOff>
-    </from>
-    <ext cx="2439489" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>385352</colOff>
-      <row>10</row>
-      <rowOff>50800</rowOff>
-    </from>
-    <ext cx="2437315" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+      <col>2</col>
       <colOff>181629</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1262342" cy="546100"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>384266</colOff>
-      <row>4</row>
-      <rowOff>50800</rowOff>
-    </from>
-    <ext cx="2439489" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>385352</colOff>
-      <row>4</row>
-      <rowOff>50800</rowOff>
-    </from>
-    <ext cx="2437315" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>384266</colOff>
       <row>8</row>
-      <rowOff>50800</rowOff>
-    </from>
-    <ext cx="2439489" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>385352</colOff>
-      <row>8</row>
-      <rowOff>50800</rowOff>
-    </from>
-    <ext cx="2437315" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>181629</colOff>
-      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1262342" cy="546100"/>
@@ -919,13 +756,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1912,8 +1749,7 @@
     <row r="40" ht="33" customHeight="1">
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>OBSERVAÇÕES: EXEMPLO DE AGRUPAMENTO DIÁRIO: dias atribuídos apenas para demonstração. Há fotos repetidas para
-completar os pares. Não é um registro diário validado.</t>
+          <t>OBSERVAÇÕES: DEMONSTRAÇÃO: dados e fotos gerais da semana transcritos do PDF Casa Bosque.</t>
         </is>
       </c>
       <c r="C40" s="23" t="n"/>
@@ -2171,18 +2007,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.714285714285714" customWidth="1" min="1" max="1"/>
     <col width="2.714285714285714" customWidth="1" min="2" max="2"/>
     <col width="4.794285714285714" customWidth="1" min="3" max="3"/>
     <col width="11.62761904761905" customWidth="1" min="4" max="4"/>
-    <col width="26.12095238095239" customWidth="1" min="5" max="5"/>
-    <col width="1.571428571428571" customWidth="1" min="6" max="6"/>
-    <col width="23.01904761904762" customWidth="1" min="7" max="7"/>
-    <col width="23.66666666666668" customWidth="1" min="8" max="8"/>
-    <col width="6.714285714285714" customWidth="1" min="9" max="9"/>
+    <col width="52.14" customWidth="1" min="5" max="5"/>
+    <col width="23.66666666666668" customWidth="1" min="6" max="6"/>
+    <col width="6.714285714285714" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="60.9" customHeight="1"/>
@@ -2203,9 +2037,7 @@
           <t>EXEC. CONCRETAGEM DA VIGA BALDRAME</t>
         </is>
       </c>
-      <c r="F2" s="23" t="n"/>
-      <c r="G2" s="23" t="n"/>
-      <c r="H2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
     </row>
     <row r="3" ht="47.25" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
@@ -2225,9 +2057,7 @@
 MONTAGEM ARMADURAS PILARES TODAS SAPATAS</t>
         </is>
       </c>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="24" t="n"/>
+      <c r="F3" s="24" t="n"/>
     </row>
     <row r="4" ht="47.25" customHeight="1">
       <c r="B4" s="32" t="inlineStr">
@@ -2247,9 +2077,7 @@
 INTERNAS VIGAS BALDRAME</t>
         </is>
       </c>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="23" t="n"/>
-      <c r="H4" s="24" t="n"/>
+      <c r="F4" s="24" t="n"/>
     </row>
     <row r="5" ht="17.22499999999999" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
@@ -2260,9 +2088,7 @@
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="18.07900000000001" customHeight="1">
       <c r="B6" s="27" t="inlineStr">
@@ -2273,9 +2099,7 @@
       <c r="C6" s="22" t="inlineStr"/>
       <c r="D6" s="23" t="n"/>
       <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
     </row>
     <row r="7" ht="18.07900000000001" customHeight="1">
       <c r="B7" s="27" t="inlineStr">
@@ -2286,9 +2110,7 @@
       <c r="C7" s="22" t="inlineStr"/>
       <c r="D7" s="23" t="n"/>
       <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
     </row>
     <row r="8" ht="18.07900000000001" customHeight="1">
       <c r="B8" s="27" t="inlineStr">
@@ -2299,9 +2121,7 @@
       <c r="C8" s="22" t="inlineStr"/>
       <c r="D8" s="23" t="n"/>
       <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n"/>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
     </row>
     <row r="9" ht="18.07899999999995" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
@@ -2312,9 +2132,7 @@
       <c r="C9" s="22" t="inlineStr"/>
       <c r="D9" s="23" t="n"/>
       <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
     </row>
     <row r="10" ht="18.07900000000001" customHeight="1">
       <c r="B10" s="27" t="inlineStr">
@@ -2325,9 +2143,7 @@
       <c r="C10" s="22" t="inlineStr"/>
       <c r="D10" s="23" t="n"/>
       <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="23" t="n"/>
-      <c r="H10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
     </row>
     <row r="11" ht="8" customHeight="1"/>
     <row r="12" ht="17.22500000000002" customHeight="1">
@@ -2339,65 +2155,48 @@
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
     </row>
     <row r="13" ht="10" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t>SEGUNDA-FEIRA • 28/09/2026 • 2 FOTOS</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="41" t="n"/>
-    </row>
-    <row r="15" ht="148" customHeight="1"/>
+          <t>EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="152" customHeight="1"/>
     <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="G16" s="42" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="178.505" customHeight="1"/>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS INTERNAS VIGAS BALDRAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="168.505" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
         </is>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>ART Nº: CE20261946083</t>
         </is>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>ALVARÁ: 216/2026</t>
         </is>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>EMPRESA: SANTELMO ENGENHARIA</t>
         </is>
@@ -2405,7 +2204,7 @@
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23" ht="14" customHeight="1">
-      <c r="B23" s="45" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>santelmoengenharia@gmail.com</t>
         </is>
@@ -2413,42 +2212,39 @@
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
     </row>
     <row r="24" ht="48.79999999999995" customHeight="1"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="D4"/>
-    <mergeCell ref="C10:H10"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="D3"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B6"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E3:H3"/>
     <mergeCell ref="B7"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="D2"/>
-    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="B8"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2462,15 +2258,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E19"/>
+  <dimension ref="B2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.714285714285714" customWidth="1" min="1" max="1"/>
-    <col width="47.4" customWidth="1" min="2" max="2"/>
-    <col width="1.571428571428571" customWidth="1" min="3" max="3"/>
-    <col width="23.01904761904762" customWidth="1" min="4" max="4"/>
-    <col width="23.66666666666668" customWidth="1" min="5" max="5"/>
-    <col width="6.714285714285714" customWidth="1" min="6" max="6"/>
+    <col width="73.41904761904762" customWidth="1" min="2" max="2"/>
+    <col width="23.66666666666668" customWidth="1" min="3" max="3"/>
+    <col width="6.714285714285714" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1"/>
@@ -2480,135 +2274,75 @@
           <t>RELATÓRIO FOTOGRÁFICO</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
     </row>
     <row r="3" ht="10.775" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t>TERÇA-FEIRA • 29/09/2026 • 4 FOTOS</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="n"/>
-      <c r="D4" s="40" t="n"/>
-      <c r="E4" s="41" t="n"/>
-    </row>
-    <row r="5" ht="148" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME
-+ MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="D6" s="47" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME
-+ MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="152" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME
-+ MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME
-+ MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>QUARTA-FEIRA • 30/09/2026 • 2 FOTOS</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="40" t="n"/>
-      <c r="E10" s="41" t="n"/>
-    </row>
-    <row r="11" ht="148" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="48" t="inlineStr">
-        <is>
-          <t>FOTO REPETIDA — SOMENTE DEMONSTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
-        <is>
-          <t>FOTO REPETIDA — SOMENTE DEMONSTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="n"/>
-    </row>
-    <row r="13" ht="84" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="43" t="inlineStr">
+          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS
+BALDRAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="152" customHeight="1"/>
+    <row r="6" ht="28" customHeight="1">
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS
+BALDRAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="440" customHeight="1"/>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="B15" s="44" t="inlineStr">
+    <row r="9" ht="13" customHeight="1">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>ART Nº: CE20261946083</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="B16" s="44" t="inlineStr">
+    <row r="10" ht="13" customHeight="1">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>ALVARÁ: 216/2026</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+    <row r="11" ht="13" customHeight="1">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>EMPRESA: SANTELMO ENGENHARIA</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="14" customHeight="1">
-      <c r="B19" s="45" t="inlineStr">
+    <row r="12" ht="8" customHeight="1"/>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>santelmoengenharia@gmail.com</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="48.79999999999995" customHeight="1"/>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="48.79999999999995" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="B12"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B6"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="D12:E12"/>
+  <mergeCells count="8">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="B10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2620,148 +2354,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6.714285714285714" customWidth="1" min="1" max="1"/>
-    <col width="47.4" customWidth="1" min="2" max="2"/>
-    <col width="1.571428571428571" customWidth="1" min="3" max="3"/>
-    <col width="23.01904761904762" customWidth="1" min="4" max="4"/>
-    <col width="23.66666666666668" customWidth="1" min="5" max="5"/>
-    <col width="6.714285714285714" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1"/>
-    <row r="2" ht="17.225" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>RELATÓRIO FOTOGRÁFICO</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="10.775" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>QUINTA-FEIRA • 01/10/2026 • 2 FOTOS</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="n"/>
-      <c r="D4" s="40" t="n"/>
-      <c r="E4" s="41" t="n"/>
-    </row>
-    <row r="5" ht="148" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) +
-ATERRO E COMPACTAÇÃO ÁREAS INTERNAS VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="D6" s="47" t="inlineStr">
-        <is>
-          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) +
-ATERRO E COMPACTAÇÃO ÁREAS INTERNAS VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>SEXTA-FEIRA • 02/10/2026 • 2 FOTOS</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="40" t="n"/>
-      <c r="E8" s="41" t="n"/>
-    </row>
-    <row r="9" ht="148" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>FOTO REPETIDA — SOMENTE DEMONSTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>FOTO REPETIDA — SOMENTE DEMONSTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="260" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="B13" s="44" t="inlineStr">
-        <is>
-          <t>ART Nº: CE20261946083</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>ALVARÁ: 216/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>EMPRESA: SANTELMO ENGENHARIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1"/>
-    <row r="17" ht="14" customHeight="1">
-      <c r="B17" s="45" t="inlineStr">
-        <is>
-          <t>santelmoengenharia@gmail.com</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="48.79999999999995" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B6"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B15:D15"/>
-  </mergeCells>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>

--- a/examples/gerados/RSO-Demonstracao.xlsx
+++ b/examples/gerados/RSO-Demonstracao.xlsx
@@ -10,12 +10,14 @@
     <sheet name="01 RSO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="02 RSO e fotos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="03 Fotos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="_Dados" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="04 Fotos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="_Dados" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'01 RSO'!$A$1:$S$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02 RSO e fotos'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02 RSO e fotos'!$A$1:$G$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03 Fotos'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'04 Fotos'!$A$1:$D$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.##%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,71 +40,98 @@
       <name val="Tw Cen MT"/>
       <b val="1"/>
       <color rgb="00009900"/>
-      <sz val="9.65"/>
+      <sz val="10.36488663975008"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="9.65"/>
+      <sz val="10.36488663975008"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="10.4"/>
+      <sz val="11.17044777755449"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="9.4"/>
+      <sz val="10.09636626048194"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="9.4"/>
+      <sz val="10.09636626048194"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="9.65"/>
+      <sz val="10.36488663975008"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
+      <sz val="8.592652136580377"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="9.666733653652923"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="12"/>
+      <sz val="12.88897820487056"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="11"/>
+      <sz val="11.81489668779802"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <b val="1"/>
       <color rgb="00548235"/>
-      <sz val="9"/>
+      <sz val="10.74081517072547"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00000000"/>
-      <sz val="9.15"/>
+      <sz val="9.827845881213806"/>
     </font>
     <font>
       <name val="Tw Cen MT"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9.9"/>
+      <sz val="10.63340701901822"/>
+    </font>
+    <font>
+      <name val="Tw Cen MT"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11.049000782187"/>
+    </font>
+    <font>
+      <name val="Tw Cen MT"/>
+      <b val="1"/>
+      <color rgb="00548235"/>
+      <sz val="10.62403921364134"/>
+    </font>
+    <font>
+      <name val="Tw Cen MT"/>
+      <color rgb="00000000"/>
+      <sz val="9.986596860822861"/>
+    </font>
+    <font>
+      <name val="Tw Cen MT"/>
+      <color rgb="00000000"/>
+      <sz val="9.720995880481826"/>
+    </font>
+    <font>
+      <name val="Tw Cen MT"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.51779882150493"/>
     </font>
   </fonts>
   <fills count="6">
@@ -133,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -227,11 +256,19 @@
         <color rgb="00737373"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="00385723"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00385723"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -317,9 +354,10 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -327,6 +365,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -410,11 +463,11 @@
   <oneCellAnchor>
     <from>
       <col>16</col>
-      <colOff>80879</colOff>
+      <colOff>15513</colOff>
       <row>0</row>
-      <rowOff>990600</rowOff>
+      <rowOff>252000</rowOff>
     </from>
-    <ext cx="1456984" cy="2056257"/>
+    <ext cx="1707643" cy="2410016"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -435,11 +488,11 @@
   <oneCellAnchor>
     <from>
       <col>15</col>
-      <colOff>29413</colOff>
+      <colOff>29123</colOff>
       <row>1</row>
-      <rowOff>15291</rowOff>
+      <rowOff>59491</rowOff>
     </from>
-    <ext cx="2012290" cy="870534"/>
+    <ext cx="2166301" cy="937161"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -460,11 +513,11 @@
   <oneCellAnchor>
     <from>
       <col>7</col>
-      <colOff>25475</colOff>
+      <colOff>18263</colOff>
       <row>16</row>
-      <rowOff>12700</rowOff>
+      <rowOff>18893</rowOff>
     </from>
-    <ext cx="262467" cy="279400"/>
+    <ext cx="300098" cy="319460"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -485,11 +538,11 @@
   <oneCellAnchor>
     <from>
       <col>7</col>
-      <colOff>25475</colOff>
+      <colOff>18263</colOff>
       <row>18</row>
-      <rowOff>12700</rowOff>
+      <rowOff>18892</rowOff>
     </from>
-    <ext cx="262467" cy="279400"/>
+    <ext cx="300098" cy="319460"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -507,6 +560,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>196175</colOff>
+      <row>16</row>
+      <rowOff>93956</rowOff>
+    </from>
+    <ext cx="169333" cy="169333"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>196175</colOff>
+      <row>18</row>
+      <rowOff>93956</rowOff>
+    </from>
+    <ext cx="169333" cy="169333"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -514,12 +617,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>155666</colOff>
+      <col>1</col>
+      <colOff>-6</colOff>
       <row>14</row>
-      <rowOff>0</rowOff>
+      <rowOff>242737</rowOff>
     </from>
-    <ext cx="2439489" cy="1828800"/>
+    <ext cx="3472957" cy="2603555"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -540,11 +643,221 @@
   <oneCellAnchor>
     <from>
       <col>4</col>
-      <colOff>2326992</colOff>
+      <colOff>2058192</colOff>
       <row>14</row>
-      <rowOff>0</rowOff>
+      <rowOff>241577</rowOff>
     </from>
-    <ext cx="2437315" cy="1828800"/>
+    <ext cx="3472957" cy="2605877"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>181481</colOff>
+      <row>16</row>
+      <rowOff>-4</rowOff>
+    </from>
+    <ext cx="1383067" cy="598327"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>-6</colOff>
+      <row>4</row>
+      <rowOff>195888</rowOff>
+    </from>
+    <ext cx="3472957" cy="2603555"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>3582077</colOff>
+      <row>4</row>
+      <rowOff>194727</rowOff>
+    </from>
+    <ext cx="3472957" cy="2605877"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>-6</colOff>
+      <row>6</row>
+      <rowOff>195896</rowOff>
+    </from>
+    <ext cx="3472957" cy="2603555"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>3582077</colOff>
+      <row>6</row>
+      <rowOff>194735</rowOff>
+    </from>
+    <ext cx="3472957" cy="2605877"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>202456</colOff>
+      <row>8</row>
+      <rowOff>-2</rowOff>
+    </from>
+    <ext cx="1341117" cy="580179"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>-6</colOff>
+      <row>4</row>
+      <rowOff>195888</rowOff>
+    </from>
+    <ext cx="3472957" cy="2603555"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>3582077</colOff>
+      <row>4</row>
+      <rowOff>194727</rowOff>
+    </from>
+    <ext cx="3472957" cy="2605877"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -565,11 +878,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>155666</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
+      <colOff>202456</colOff>
+      <row>6</row>
+      <rowOff>-2</rowOff>
     </from>
-    <ext cx="2439489" cy="1828800"/>
+    <ext cx="1341117" cy="580179"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -577,186 +890,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>2326992</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2437315" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>181629</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1262342" cy="546100"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>384266</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2439489" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>3745772</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2437315" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>384266</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2439489" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>3745772</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2437315" cy="1828800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>181629</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1262342" cy="546100"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1062,65 +1195,65 @@
   <dimension ref="B2:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.714285714285714" customWidth="1" min="1" max="1"/>
-    <col width="3.095238095238095" customWidth="1" min="2" max="2"/>
-    <col width="4.238095238095238" customWidth="1" min="3" max="3"/>
-    <col width="0.1022222222222224" customWidth="1" min="4" max="4"/>
-    <col width="1.396190476190476" customWidth="1" min="5" max="5"/>
-    <col width="0.4444444444444444" customWidth="1" min="6" max="6"/>
-    <col width="4.047619047619048" customWidth="1" min="7" max="7"/>
-    <col width="3.993333333333335" customWidth="1" min="8" max="8"/>
-    <col width="2.785714285714286" customWidth="1" min="9" max="9"/>
-    <col width="1.302476190476189" customWidth="1" min="10" max="10"/>
-    <col width="4.50704761904762" customWidth="1" min="11" max="11"/>
-    <col width="27.41428571428571" customWidth="1" min="12" max="12"/>
-    <col width="5.190476190476191" customWidth="1" min="13" max="13"/>
-    <col width="0.1372222222222237" customWidth="1" min="14" max="14"/>
-    <col width="0.6405555555555541" customWidth="1" min="15" max="15"/>
-    <col width="6.187619047619051" customWidth="1" min="16" max="16"/>
-    <col width="16.27619047619049" customWidth="1" min="17" max="17"/>
-    <col width="6.523809523809524" customWidth="1" min="18" max="18"/>
-    <col width="6.714285714285714" customWidth="1" min="19" max="19"/>
+    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
+    <col width="3.377333333333333" customWidth="1" min="2" max="2"/>
+    <col width="4.604952380952382" customWidth="1" min="3" max="3"/>
+    <col width="0.1098888888888894" customWidth="1" min="4" max="4"/>
+    <col width="1.552380952380951" customWidth="1" min="5" max="5"/>
+    <col width="0.4774444444444457" customWidth="1" min="6" max="6"/>
+    <col width="4.40038095238095" customWidth="1" min="7" max="7"/>
+    <col width="4.342095238095239" customWidth="1" min="8" max="8"/>
+    <col width="3.044952380952379" customWidth="1" min="9" max="9"/>
+    <col width="1.452000000000004" customWidth="1" min="10" max="10"/>
+    <col width="4.893714285714282" customWidth="1" min="11" max="11"/>
+    <col width="29.49809523809524" customWidth="1" min="12" max="12"/>
+    <col width="5.627809523809523" customWidth="1" min="13" max="13"/>
+    <col width="0.1474444444444442" customWidth="1" min="14" max="14"/>
+    <col width="0.6880000000000007" customWidth="1" min="15" max="15"/>
+    <col width="6.698857142857139" customWidth="1" min="16" max="16"/>
+    <col width="17.53485714285715" customWidth="1" min="17" max="17"/>
+    <col width="7.059999999999989" customWidth="1" min="18" max="18"/>
+    <col width="3.065333333333348" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="89" customHeight="1"/>
-    <row r="2" ht="13.59999999999999" customHeight="1">
+    <row r="1" ht="32.735" customHeight="1"/>
+    <row r="2" ht="15.94" customHeight="1">
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>SANTELMO ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.60000000000001" customHeight="1">
+    <row r="3" ht="15.93900000000001" customHeight="1">
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>CNPJ: 26.913.287/0001-34</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="13.60000000000001" customHeight="1">
+    <row r="4" ht="15.94" customHeight="1">
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Rua Crescêncio Ferreira, nº 1726 - Bairro Morada do Sol - Teresina (PI)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.59999999999999" customHeight="1">
+    <row r="5" ht="15.94" customHeight="1">
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>E-mail: santelmoengenharia@gmail.com</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="13.59999999999999" customHeight="1">
+    <row r="6" ht="15.94" customHeight="1">
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Fone: (86) 3011-2104</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="5.224999999999994" customHeight="1"/>
-    <row r="8" ht="17.22499999999999" customHeight="1">
+    <row r="7" ht="6.124000000000009" customHeight="1"/>
+    <row r="8" ht="20.188" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>RELATÓRIO SEMANAL DE OBRA (RSO)</t>
@@ -1143,8 +1276,8 @@
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="5" t="n"/>
     </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="13.60000000000002" customHeight="1">
+    <row r="9" ht="7.031999999999982" customHeight="1"/>
+    <row r="10" ht="15.94" customHeight="1">
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>OBRA:</t>
@@ -1156,7 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="13.59999999999999" customHeight="1">
+    <row r="11" ht="15.94" customHeight="1">
       <c r="B11" s="6" t="inlineStr">
         <is>
           <t>CLIENTE:</t>
@@ -1168,7 +1301,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="13.59999999999999" customHeight="1">
+    <row r="12" ht="15.93900000000002" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
           <t>RESPONS. TÉCNICO:</t>
@@ -1180,7 +1313,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="13.59999999999999" customHeight="1">
+    <row r="13" ht="15.94" customHeight="1">
       <c r="B13" s="6" t="inlineStr">
         <is>
           <t>REFERÊNCIA:</t>
@@ -1192,8 +1325,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="7.400000000000006" customHeight="1"/>
-    <row r="15" ht="13.60000000000002" customHeight="1">
+    <row r="14" ht="8.673000000000002" customHeight="1"/>
+    <row r="15" ht="15.94" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>TEMPO PREDOMINANTE</t>
@@ -1224,8 +1357,8 @@
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="5" t="n"/>
     </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="13" customHeight="1">
+    <row r="16" ht="7.031999999999982" customHeight="1"/>
+    <row r="17" ht="15.23699999999999" customHeight="1">
       <c r="B17" s="9" t="inlineStr">
         <is>
           <t>MANHÃ</t>
@@ -1241,7 +1374,7 @@
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Sim [ ]</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="L17" s="10" t="n"/>
@@ -1249,7 +1382,7 @@
       <c r="N17" s="10" t="n"/>
       <c r="O17" s="11" t="n"/>
     </row>
-    <row r="18" ht="11" customHeight="1">
+    <row r="18" ht="12.892" customHeight="1">
       <c r="B18" s="14" t="n"/>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="15" t="n"/>
@@ -1270,7 +1403,7 @@
       <c r="Q18" s="10" t="n"/>
       <c r="R18" s="11" t="n"/>
     </row>
-    <row r="19" ht="11" customHeight="1">
+    <row r="19" ht="12.89300000000003" customHeight="1">
       <c r="B19" s="9" t="inlineStr">
         <is>
           <t>TARDE</t>
@@ -1286,7 +1419,7 @@
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Não [X]</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="L19" s="10" t="n"/>
@@ -1297,7 +1430,7 @@
       <c r="Q19" s="15" t="n"/>
       <c r="R19" s="16" t="n"/>
     </row>
-    <row r="20" ht="13" customHeight="1">
+    <row r="20" ht="15.23599999999999" customHeight="1">
       <c r="B20" s="14" t="n"/>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
@@ -1313,8 +1446,8 @@
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="16" t="n"/>
     </row>
-    <row r="21" ht="11.02999999999997" customHeight="1"/>
-    <row r="22" ht="13.60000000000002" customHeight="1">
+    <row r="21" ht="12.928" customHeight="1"/>
+    <row r="22" ht="15.94" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>FUNCIONÁRIOS DA SANTELMO</t>
@@ -1345,7 +1478,7 @@
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="5" t="n"/>
     </row>
-    <row r="23" ht="13.59999999999997" customHeight="1">
+    <row r="23" ht="15.93900000000002" customHeight="1">
       <c r="B23" s="18" t="inlineStr">
         <is>
           <t>FUNÇÃO / CARGO</t>
@@ -1388,7 +1521,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="13.60000000000002" customHeight="1">
+    <row r="24" ht="15.94" customHeight="1">
       <c r="B24" s="22" t="inlineStr">
         <is>
           <t>ENG. CIVIL</t>
@@ -1413,7 +1546,7 @@
       <c r="Q24" s="24" t="n"/>
       <c r="R24" s="27" t="inlineStr"/>
     </row>
-    <row r="25" ht="13.59999999999997" customHeight="1">
+    <row r="25" ht="15.94" customHeight="1">
       <c r="B25" s="22" t="inlineStr">
         <is>
           <t>ENG. ELETRICISTA</t>
@@ -1438,7 +1571,7 @@
       <c r="Q25" s="24" t="n"/>
       <c r="R25" s="27" t="inlineStr"/>
     </row>
-    <row r="26" ht="13.60000000000002" customHeight="1">
+    <row r="26" ht="15.94" customHeight="1">
       <c r="B26" s="22" t="inlineStr">
         <is>
           <t>ESTAGIÁRIO</t>
@@ -1463,7 +1596,7 @@
       <c r="Q26" s="24" t="n"/>
       <c r="R26" s="27" t="inlineStr"/>
     </row>
-    <row r="27" ht="13.60000000000002" customHeight="1">
+    <row r="27" ht="15.93899999999996" customHeight="1">
       <c r="B27" s="22" t="inlineStr">
         <is>
           <t>MESTRE DE OBRAS</t>
@@ -1488,7 +1621,7 @@
       <c r="Q27" s="24" t="n"/>
       <c r="R27" s="27" t="inlineStr"/>
     </row>
-    <row r="28" ht="13.59999999999997" customHeight="1">
+    <row r="28" ht="15.94000000000005" customHeight="1">
       <c r="B28" s="22" t="inlineStr">
         <is>
           <t>PEDREIRO</t>
@@ -1513,7 +1646,7 @@
       <c r="Q28" s="24" t="n"/>
       <c r="R28" s="27" t="inlineStr"/>
     </row>
-    <row r="29" ht="13.60000000000002" customHeight="1">
+    <row r="29" ht="15.94" customHeight="1">
       <c r="B29" s="22" t="inlineStr">
         <is>
           <t>ELETRICISTA</t>
@@ -1538,7 +1671,7 @@
       <c r="Q29" s="24" t="n"/>
       <c r="R29" s="27" t="inlineStr"/>
     </row>
-    <row r="30" ht="13.59999999999997" customHeight="1">
+    <row r="30" ht="15.94" customHeight="1">
       <c r="B30" s="22" t="inlineStr">
         <is>
           <t>SERVENTE</t>
@@ -1563,7 +1696,7 @@
       <c r="Q30" s="24" t="n"/>
       <c r="R30" s="27" t="inlineStr"/>
     </row>
-    <row r="31" ht="13.60000000000002" customHeight="1">
+    <row r="31" ht="15.93899999999996" customHeight="1">
       <c r="B31" s="22" t="inlineStr">
         <is>
           <t>CARPINTEIRO</t>
@@ -1588,7 +1721,7 @@
       <c r="Q31" s="24" t="n"/>
       <c r="R31" s="27" t="inlineStr"/>
     </row>
-    <row r="32" ht="13.60000000000002" customHeight="1">
+    <row r="32" ht="15.94" customHeight="1">
       <c r="B32" s="22" t="inlineStr">
         <is>
           <t>FERREIRO</t>
@@ -1613,7 +1746,7 @@
       <c r="Q32" s="24" t="n"/>
       <c r="R32" s="27" t="inlineStr"/>
     </row>
-    <row r="33" ht="13.59999999999997" customHeight="1">
+    <row r="33" ht="15.94" customHeight="1">
       <c r="B33" s="22" t="inlineStr">
         <is>
           <t>BOMBEIRO HIDRÁULICO</t>
@@ -1638,7 +1771,7 @@
       <c r="Q33" s="24" t="n"/>
       <c r="R33" s="27" t="inlineStr"/>
     </row>
-    <row r="34" ht="13.60000000000002" customHeight="1">
+    <row r="34" ht="15.94000000000005" customHeight="1">
       <c r="B34" s="22" t="inlineStr">
         <is>
           <t>PINTOR</t>
@@ -1663,7 +1796,7 @@
       <c r="Q34" s="24" t="n"/>
       <c r="R34" s="27" t="inlineStr"/>
     </row>
-    <row r="35" ht="13.59999999999997" customHeight="1">
+    <row r="35" ht="15.93899999999996" customHeight="1">
       <c r="B35" s="22" t="inlineStr"/>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -1682,7 +1815,7 @@
       <c r="Q35" s="24" t="n"/>
       <c r="R35" s="27" t="inlineStr"/>
     </row>
-    <row r="36" ht="13.60000000000002" customHeight="1">
+    <row r="36" ht="15.94000000000005" customHeight="1">
       <c r="B36" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -1719,8 +1852,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="47.66999999999996" customHeight="1"/>
-    <row r="38" ht="13.60000000000002" customHeight="1">
+    <row r="37" ht="55.87099999999998" customHeight="1"/>
+    <row r="38" ht="15.93999999999994" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
           <t>TOTAL DE FUNCIONÁRIOS: 4</t>
@@ -1745,8 +1878,8 @@
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="5" t="n"/>
     </row>
-    <row r="39" ht="11.39999999999998" customHeight="1"/>
-    <row r="40" ht="33" customHeight="1">
+    <row r="39" ht="13.36099999999999" customHeight="1"/>
+    <row r="40" ht="38.67700000000002" customHeight="1">
       <c r="B40" s="22" t="inlineStr">
         <is>
           <t>OBSERVAÇÕES: DEMONSTRAÇÃO: dados e fotos gerais da semana transcritos do PDF Casa Bosque.</t>
@@ -1769,8 +1902,8 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="24" t="n"/>
     </row>
-    <row r="41" ht="6.600000000000023" customHeight="1"/>
-    <row r="42" ht="17.22500000000002" customHeight="1">
+    <row r="41" ht="7.73599999999999" customHeight="1"/>
+    <row r="42" ht="20.18799999999999" customHeight="1">
       <c r="B42" s="3" t="inlineStr">
         <is>
           <t>DIA</t>
@@ -1797,7 +1930,7 @@
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="5" t="n"/>
     </row>
-    <row r="43" ht="51.5" customHeight="1">
+    <row r="43" ht="60.36000000000001" customHeight="1">
       <c r="B43" s="32" t="inlineStr">
         <is>
           <t>28</t>
@@ -1828,7 +1961,7 @@
       <c r="Q43" s="23" t="n"/>
       <c r="R43" s="24" t="n"/>
     </row>
-    <row r="44" ht="51.5" customHeight="1">
+    <row r="44" ht="60.36000000000001" customHeight="1">
       <c r="B44" s="32" t="inlineStr">
         <is>
           <t>29</t>
@@ -1860,7 +1993,7 @@
       <c r="Q44" s="23" t="n"/>
       <c r="R44" s="24" t="n"/>
     </row>
-    <row r="45" ht="79.42499999999995" customHeight="1"/>
+    <row r="45" ht="19.84299999999996" customHeight="1"/>
   </sheetData>
   <mergeCells count="122">
     <mergeCell ref="P18:R19"/>
@@ -2007,20 +2140,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F23"/>
+  <dimension ref="B2:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.714285714285714" customWidth="1" min="1" max="1"/>
-    <col width="2.714285714285714" customWidth="1" min="2" max="2"/>
-    <col width="4.794285714285714" customWidth="1" min="3" max="3"/>
-    <col width="11.62761904761905" customWidth="1" min="4" max="4"/>
-    <col width="52.14" customWidth="1" min="5" max="5"/>
-    <col width="23.66666666666668" customWidth="1" min="6" max="6"/>
-    <col width="6.714285714285714" customWidth="1" min="7" max="7"/>
+    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
+    <col width="2.968190476190477" customWidth="1" min="2" max="2"/>
+    <col width="5.202476190476191" customWidth="1" min="3" max="3"/>
+    <col width="12.54190476190476" customWidth="1" min="4" max="4"/>
+    <col width="56.05542857142858" customWidth="1" min="5" max="5"/>
+    <col width="25.4727619047619" customWidth="1" min="6" max="6"/>
+    <col width="3.065333333333348" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.9" customHeight="1"/>
-    <row r="2" ht="47.25000000000001" customHeight="1">
+    <row r="1" ht="19.843" customHeight="1"/>
+    <row r="2" ht="51.768" customHeight="1">
       <c r="B2" s="32" t="inlineStr">
         <is>
           <t>30</t>
@@ -2039,7 +2172,7 @@
       </c>
       <c r="F2" s="24" t="n"/>
     </row>
-    <row r="3" ht="47.25" customHeight="1">
+    <row r="3" ht="51.76899999999999" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
           <t>01</t>
@@ -2059,7 +2192,7 @@
       </c>
       <c r="F3" s="24" t="n"/>
     </row>
-    <row r="4" ht="47.25" customHeight="1">
+    <row r="4" ht="51.76900000000001" customHeight="1">
       <c r="B4" s="32" t="inlineStr">
         <is>
           <t>02</t>
@@ -2079,7 +2212,7 @@
       </c>
       <c r="F4" s="24" t="n"/>
     </row>
-    <row r="5" ht="17.22499999999999" customHeight="1">
+    <row r="5" ht="18.87199999999999" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CHEGADA DE MATERIAIS</t>
@@ -2090,7 +2223,7 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
-    <row r="6" ht="18.07900000000001" customHeight="1">
+    <row r="6" ht="19.80800000000002" customHeight="1">
       <c r="B6" s="27" t="inlineStr">
         <is>
           <t>1)</t>
@@ -2101,7 +2234,7 @@
       <c r="E6" s="23" t="n"/>
       <c r="F6" s="24" t="n"/>
     </row>
-    <row r="7" ht="18.07900000000001" customHeight="1">
+    <row r="7" ht="19.80799999999999" customHeight="1">
       <c r="B7" s="27" t="inlineStr">
         <is>
           <t>2)</t>
@@ -2112,7 +2245,7 @@
       <c r="E7" s="23" t="n"/>
       <c r="F7" s="24" t="n"/>
     </row>
-    <row r="8" ht="18.07900000000001" customHeight="1">
+    <row r="8" ht="19.80799999999999" customHeight="1">
       <c r="B8" s="27" t="inlineStr">
         <is>
           <t>3)</t>
@@ -2123,7 +2256,7 @@
       <c r="E8" s="23" t="n"/>
       <c r="F8" s="24" t="n"/>
     </row>
-    <row r="9" ht="18.07899999999995" customHeight="1">
+    <row r="9" ht="19.80799999999999" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
         <is>
           <t>4)</t>
@@ -2134,7 +2267,7 @@
       <c r="E9" s="23" t="n"/>
       <c r="F9" s="24" t="n"/>
     </row>
-    <row r="10" ht="18.07900000000001" customHeight="1">
+    <row r="10" ht="19.80799999999999" customHeight="1">
       <c r="B10" s="27" t="inlineStr">
         <is>
           <t>5)</t>
@@ -2145,8 +2278,8 @@
       <c r="E10" s="23" t="n"/>
       <c r="F10" s="24" t="n"/>
     </row>
-    <row r="11" ht="8" customHeight="1"/>
-    <row r="12" ht="17.22500000000002" customHeight="1">
+    <row r="11" ht="8.765000000000043" customHeight="1"/>
+    <row r="12" ht="18.87299999999999" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>RELATÓRIO FOTOGRÁFICO</t>
@@ -2157,66 +2290,62 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="5" t="n"/>
     </row>
-    <row r="13" ht="10" customHeight="1"/>
-    <row r="14" ht="24" customHeight="1">
+    <row r="13" ht="10.95599999999996" customHeight="1"/>
+    <row r="14" ht="30.67800000000005" customHeight="1">
       <c r="B14" s="39" t="inlineStr">
         <is>
           <t>EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="152" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS INTERNAS VIGAS BALDRAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="168.505" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="40" t="inlineStr">
+      <c r="C14" s="40" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="40" t="n"/>
+    </row>
+    <row r="15" ht="373.069" customHeight="1"/>
+    <row r="16" ht="19.72199999999998" customHeight="1">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="B19" s="41" t="inlineStr">
+    <row r="17" ht="14.24299999999994" customHeight="1">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>ART Nº: CE20261946083</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="B20" s="41" t="inlineStr">
+    <row r="18" ht="14.24300000000005" customHeight="1">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>ALVARÁ: 216/2026</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="B21" s="41" t="inlineStr">
+    <row r="19" ht="14.24299999999994" customHeight="1">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>EMPRESA: SANTELMO ENGENHARIA</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="8" customHeight="1"/>
-    <row r="23" ht="14" customHeight="1">
-      <c r="B23" s="42" t="inlineStr">
+    <row r="20" ht="8.766000000000076" customHeight="1"/>
+    <row r="21" ht="15.33799999999997" customHeight="1">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>santelmoengenharia@gmail.com</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="48.79999999999995" customHeight="1"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="19.84299999999996" customHeight="1"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
     <mergeCell ref="D4"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="D3"/>
@@ -2225,21 +2354,20 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B6"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="D2"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="B19:E19"/>
@@ -2261,78 +2389,80 @@
   <dimension ref="B2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.714285714285714" customWidth="1" min="1" max="1"/>
-    <col width="73.41904761904762" customWidth="1" min="2" max="2"/>
-    <col width="23.66666666666668" customWidth="1" min="3" max="3"/>
-    <col width="6.714285714285714" customWidth="1" min="4" max="4"/>
+    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
+    <col width="78.91085714285714" customWidth="1" min="2" max="2"/>
+    <col width="25.4727619047619" customWidth="1" min="3" max="3"/>
+    <col width="3.065333333333348" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1"/>
-    <row r="2" ht="17.225" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1" ht="19.843" customHeight="1"/>
+    <row r="2" ht="18.299" customHeight="1">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>RELATÓRIO FOTOGRÁFICO</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
     </row>
-    <row r="3" ht="10.775" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS
-BALDRAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="152" customHeight="1"/>
-    <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS
-BALDRAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="440" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="40" t="inlineStr">
+    <row r="3" ht="11.448" customHeight="1"/>
+    <row r="4" ht="36.122" customHeight="1">
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS INTERNAS
+VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="n"/>
+    </row>
+    <row r="5" ht="244.352" customHeight="1"/>
+    <row r="6" ht="36.12199999999996" customHeight="1">
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM
+VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n"/>
+    </row>
+    <row r="7" ht="371.842" customHeight="1"/>
+    <row r="8" ht="19.12299999999993" customHeight="1">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="B9" s="41" t="inlineStr">
+    <row r="9" ht="13.81100000000004" customHeight="1">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>ART Nº: CE20261946083</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="B10" s="41" t="inlineStr">
+    <row r="10" ht="13.81100000000004" customHeight="1">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>ALVARÁ: 216/2026</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="B11" s="41" t="inlineStr">
+    <row r="11" ht="13.81200000000001" customHeight="1">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>EMPRESA: SANTELMO ENGENHARIA</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="14" customHeight="1">
-      <c r="B13" s="42" t="inlineStr">
+    <row r="12" ht="8.49899999999991" customHeight="1"/>
+    <row r="13" ht="14.87300000000005" customHeight="1">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>santelmoengenharia@gmail.com</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
     </row>
-    <row r="14" ht="48.79999999999995" customHeight="1"/>
+    <row r="14" ht="19.84299999999996" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B13:C13"/>
@@ -2354,6 +2484,95 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
+    <col width="78.91085714285714" customWidth="1" min="2" max="2"/>
+    <col width="25.4727619047619" customWidth="1" min="3" max="3"/>
+    <col width="3.065333333333348" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.843" customHeight="1"/>
+    <row r="2" ht="18.299" customHeight="1">
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>RELATÓRIO FOTOGRÁFICO</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="11.448" customHeight="1"/>
+    <row r="4" ht="36.122" customHeight="1">
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM
+VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="n"/>
+    </row>
+    <row r="5" ht="652.316" customHeight="1"/>
+    <row r="6" ht="19.12299999999993" customHeight="1">
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.81100000000004" customHeight="1">
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>ART Nº: CE20261946083</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.81100000000004" customHeight="1">
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>ALVARÁ: 216/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.81200000000001" customHeight="1">
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>EMPRESA: SANTELMO ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="8.49899999999991" customHeight="1"/>
+    <row r="11" ht="14.87300000000005" customHeight="1">
+      <c r="B11" s="48" t="inlineStr">
+        <is>
+          <t>santelmoengenharia@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="19.84299999999996" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>

--- a/examples/gerados/RSO-Demonstracao.xlsx
+++ b/examples/gerados/RSO-Demonstracao.xlsx
@@ -7,17 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01 RSO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02 RSO e fotos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03 Fotos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04 Fotos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="_Dados" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="RSO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_Dados" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'01 RSO'!$A$1:$S$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'02 RSO e fotos'!$A$1:$G$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'03 Fotos'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'04 Fotos'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'RSO'!$A$1:$V$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.##%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,33 +99,6 @@
       <name val="Tw Cen MT"/>
       <color rgb="00FFFFFF"/>
       <sz val="10.63340701901822"/>
-    </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11.049000782187"/>
-    </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <b val="1"/>
-      <color rgb="00548235"/>
-      <sz val="10.62403921364134"/>
-    </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <color rgb="00000000"/>
-      <sz val="9.986596860822861"/>
-    </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <color rgb="00000000"/>
-      <sz val="9.720995880481826"/>
-    </font>
-    <font>
-      <name val="Tw Cen MT"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10.51779882150493"/>
     </font>
   </fonts>
   <fills count="6">
@@ -268,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -301,6 +268,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -324,9 +294,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -334,9 +301,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,9 +315,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -365,21 +326,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -462,12 +408,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>16</col>
-      <colOff>15513</colOff>
+      <col>19</col>
+      <colOff>86875</colOff>
       <row>0</row>
       <rowOff>252000</rowOff>
     </from>
-    <ext cx="1707643" cy="2410016"/>
+    <ext cx="1564919" cy="2208588"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -487,12 +433,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>15</col>
-      <colOff>29123</colOff>
+      <col>17</col>
+      <colOff>31591</colOff>
       <row>1</row>
-      <rowOff>59491</rowOff>
+      <rowOff>16429</rowOff>
     </from>
-    <ext cx="2166301" cy="937161"/>
+    <ext cx="2161364" cy="935025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -512,12 +458,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
-      <colOff>18263</colOff>
+      <col>8</col>
+      <colOff>27357</colOff>
       <row>16</row>
-      <rowOff>18893</rowOff>
+      <rowOff>13638</rowOff>
     </from>
-    <ext cx="300098" cy="319460"/>
+    <ext cx="281911" cy="300098"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -537,12 +483,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
-      <colOff>18263</colOff>
+      <col>8</col>
+      <colOff>27357</colOff>
       <row>18</row>
-      <rowOff>18892</rowOff>
+      <rowOff>13638</rowOff>
     </from>
-    <ext cx="300098" cy="319460"/>
+    <ext cx="281911" cy="300098"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -562,12 +508,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
-      <colOff>196175</colOff>
-      <row>16</row>
-      <rowOff>93956</rowOff>
+      <col>1</col>
+      <colOff>-6</colOff>
+      <row>58</row>
+      <rowOff>212356</rowOff>
     </from>
-    <ext cx="169333" cy="169333"/>
+    <ext cx="3472957" cy="2603555"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -587,12 +533,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
-      <colOff>196175</colOff>
-      <row>18</row>
-      <rowOff>93956</rowOff>
+      <col>13</col>
+      <colOff>844668</colOff>
+      <row>58</row>
+      <rowOff>211195</rowOff>
     </from>
-    <ext cx="169333" cy="169333"/>
+    <ext cx="3472957" cy="2605877"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -610,26 +556,21 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>-6</colOff>
-      <row>14</row>
-      <rowOff>242737</rowOff>
+      <row>61</row>
+      <rowOff>212350</rowOff>
     </from>
     <ext cx="3472957" cy="2603555"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -642,99 +583,19 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
-      <colOff>2058192</colOff>
-      <row>14</row>
-      <rowOff>241577</rowOff>
+      <col>13</col>
+      <colOff>844668</colOff>
+      <row>61</row>
+      <rowOff>211189</rowOff>
     </from>
     <ext cx="3472957" cy="2605877"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>181481</colOff>
-      <row>16</row>
-      <rowOff>-4</rowOff>
-    </from>
-    <ext cx="1383067" cy="598327"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>-6</colOff>
-      <row>4</row>
-      <rowOff>195888</rowOff>
-    </from>
-    <ext cx="3472957" cy="2603555"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>3582077</colOff>
-      <row>4</row>
-      <rowOff>194727</rowOff>
-    </from>
-    <ext cx="3472957" cy="2605877"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -749,17 +610,42 @@
     <from>
       <col>1</col>
       <colOff>-6</colOff>
-      <row>6</row>
-      <rowOff>195896</rowOff>
+      <row>64</row>
+      <rowOff>212357</rowOff>
     </from>
     <ext cx="3472957" cy="2603555"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>844668</colOff>
+      <row>64</row>
+      <rowOff>211196</rowOff>
+    </from>
+    <ext cx="3472957" cy="2605877"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -773,18 +659,18 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>3582077</colOff>
-      <row>6</row>
-      <rowOff>194735</rowOff>
+      <colOff>-6</colOff>
+      <row>67</row>
+      <rowOff>212351</rowOff>
     </from>
-    <ext cx="3472957" cy="2605877"/>
+    <ext cx="3472957" cy="2603555"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -797,49 +683,19 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>202456</colOff>
-      <row>8</row>
-      <rowOff>-2</rowOff>
+      <col>13</col>
+      <colOff>844668</colOff>
+      <row>67</row>
+      <rowOff>211190</rowOff>
     </from>
-    <ext cx="1341117" cy="580179"/>
+    <ext cx="3472957" cy="2605877"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>-6</colOff>
-      <row>4</row>
-      <rowOff>195888</rowOff>
-    </from>
-    <ext cx="3472957" cy="2603555"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -852,19 +708,19 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>3582077</colOff>
-      <row>4</row>
-      <rowOff>194727</rowOff>
+      <col>19</col>
+      <colOff>184176</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="3472957" cy="2605877"/>
+    <ext cx="1355858" cy="586556"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -877,19 +733,44 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>202456</colOff>
-      <row>6</row>
-      <rowOff>-2</rowOff>
+      <col>12</col>
+      <colOff>196175</colOff>
+      <row>16</row>
+      <rowOff>79021</rowOff>
     </from>
-    <ext cx="1341117" cy="580179"/>
+    <ext cx="169333" cy="169333"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>196175</colOff>
+      <row>18</row>
+      <rowOff>79020</rowOff>
+    </from>
+    <ext cx="169333" cy="169333"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,68 +1073,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:R44"/>
+  <dimension ref="B2:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
-    <col width="3.377333333333333" customWidth="1" min="2" max="2"/>
-    <col width="4.604952380952382" customWidth="1" min="3" max="3"/>
-    <col width="0.1098888888888894" customWidth="1" min="4" max="4"/>
-    <col width="1.552380952380951" customWidth="1" min="5" max="5"/>
-    <col width="0.4774444444444457" customWidth="1" min="6" max="6"/>
-    <col width="4.40038095238095" customWidth="1" min="7" max="7"/>
-    <col width="4.342095238095239" customWidth="1" min="8" max="8"/>
-    <col width="3.044952380952379" customWidth="1" min="9" max="9"/>
-    <col width="1.452000000000004" customWidth="1" min="10" max="10"/>
-    <col width="4.893714285714282" customWidth="1" min="11" max="11"/>
-    <col width="29.49809523809524" customWidth="1" min="12" max="12"/>
-    <col width="5.627809523809523" customWidth="1" min="13" max="13"/>
-    <col width="0.1474444444444442" customWidth="1" min="14" max="14"/>
-    <col width="0.6880000000000007" customWidth="1" min="15" max="15"/>
-    <col width="6.698857142857139" customWidth="1" min="16" max="16"/>
-    <col width="17.53485714285715" customWidth="1" min="17" max="17"/>
-    <col width="7.059999999999989" customWidth="1" min="18" max="18"/>
-    <col width="3.065333333333348" customWidth="1" min="19" max="19"/>
+    <col width="2.968190476190477" customWidth="1" min="2" max="2"/>
+    <col width="0.2386666666666662" customWidth="1" min="3" max="3"/>
+    <col width="4.604952380952382" customWidth="1" min="4" max="4"/>
+    <col width="0.1098888888888894" customWidth="1" min="5" max="5"/>
+    <col width="1.552380952380951" customWidth="1" min="6" max="6"/>
+    <col width="0.4774444444444457" customWidth="1" min="7" max="7"/>
+    <col width="4.40038095238095" customWidth="1" min="8" max="8"/>
+    <col width="4.342095238095239" customWidth="1" min="9" max="9"/>
+    <col width="3.044952380952379" customWidth="1" min="10" max="10"/>
+    <col width="1.452000000000004" customWidth="1" min="11" max="11"/>
+    <col width="4.893714285714282" customWidth="1" min="12" max="12"/>
+    <col width="5.952761904761907" customWidth="1" min="13" max="13"/>
+    <col width="22.83104761904762" customWidth="1" min="14" max="14"/>
+    <col width="5.627809523809523" customWidth="1" min="15" max="15"/>
+    <col width="0.1474444444444442" customWidth="1" min="16" max="16"/>
+    <col width="0.6880000000000007" customWidth="1" min="17" max="17"/>
+    <col width="6.535238095238095" customWidth="1" min="18" max="18"/>
+    <col width="0.09544444444444228" customWidth="1" min="19" max="19"/>
+    <col width="17.53485714285715" customWidth="1" min="20" max="20"/>
+    <col width="7.059999999999989" customWidth="1" min="21" max="21"/>
+    <col width="3.065333333333348" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.735" customHeight="1"/>
-    <row r="2" ht="15.94" customHeight="1">
-      <c r="C2" s="1" t="inlineStr">
+    <row r="1" ht="31.657" customHeight="1"/>
+    <row r="2" ht="14.608" customHeight="1">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>SANTELMO ENGENHARIA LTDA</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.93900000000001" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="3" ht="14.607" customHeight="1">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>CNPJ: 26.913.287/0001-34</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.94" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="4" ht="14.608" customHeight="1">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Rua Crescêncio Ferreira, nº 1726 - Bairro Morada do Sol - Teresina (PI)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15.94" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="5" ht="14.607" customHeight="1">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>E-mail: santelmoengenharia@gmail.com</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15.94" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="6" ht="14.60799999999999" customHeight="1">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Fone: (86) 3011-2104</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="6.124000000000009" customHeight="1"/>
-    <row r="8" ht="20.188" customHeight="1">
+    <row r="7" ht="5.612000000000009" customHeight="1"/>
+    <row r="8" ht="18.50099999999999" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>RELATÓRIO SEMANAL DE OBRA (RSO)</t>
@@ -1274,59 +1158,62 @@
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="7.031999999999982" customHeight="1"/>
-    <row r="10" ht="15.94" customHeight="1">
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="6.444999999999993" customHeight="1"/>
+    <row r="10" ht="14.60700000000003" customHeight="1">
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>OBRA:</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>EXECUÇÃO DE EDIFICAÇÃO RESIDENCIAL UNIFAMILIAR - CASA BOSQUE</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15.94" customHeight="1">
+    <row r="11" ht="14.60799999999998" customHeight="1">
       <c r="B11" s="6" t="inlineStr">
         <is>
           <t>CLIENTE:</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>DANILO FONSECA</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.93900000000002" customHeight="1">
+    <row r="12" ht="14.607" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
           <t>RESPONS. TÉCNICO:</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>ENGº DANILO JOSÉ FONSECA LIMA</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.94" customHeight="1">
+    <row r="13" ht="14.608" customHeight="1">
       <c r="B13" s="6" t="inlineStr">
         <is>
           <t>REFERÊNCIA:</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>DE 28/09/2026 A 02/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="8.673000000000002" customHeight="1"/>
-    <row r="15" ht="15.94" customHeight="1">
+    <row r="14" ht="7.948000000000008" customHeight="1"/>
+    <row r="15" ht="14.607" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>TEMPO PREDOMINANTE</t>
@@ -1339,26 +1226,29 @@
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>FERIADOS NA SEMANA?</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="8" t="inlineStr">
         <is>
           <t>EVOLUÇÃO DA OBRA</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="7.031999999999982" customHeight="1"/>
-    <row r="17" ht="15.23699999999999" customHeight="1">
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="6.444999999999993" customHeight="1"/>
+    <row r="17" ht="13.96299999999999" customHeight="1">
       <c r="B17" s="9" t="inlineStr">
         <is>
           <t>MANHÃ</t>
@@ -1366,44 +1256,49 @@
       </c>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="12" t="inlineStr"/>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="L17" s="10" t="n"/>
       <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="12.892" customHeight="1">
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
+      <c r="N17" s="14" t="inlineStr"/>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="11.81500000000003" customHeight="1">
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
-      <c r="F18" s="14" t="n"/>
+      <c r="F18" s="17" t="n"/>
       <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
       <c r="J18" s="16" t="n"/>
-      <c r="K18" s="14" t="n"/>
+      <c r="K18" s="17" t="n"/>
       <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
       <c r="O18" s="16" t="n"/>
-      <c r="P18" s="17" t="n">
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="17" t="n"/>
+      <c r="R18" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="12.89300000000003" customHeight="1">
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="11.815" customHeight="1">
       <c r="B19" s="9" t="inlineStr">
         <is>
           <t>TARDE</t>
@@ -1411,43 +1306,48 @@
       </c>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="12" t="inlineStr"/>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="13" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="15" t="n"/>
-      <c r="R19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="15.23599999999999" customHeight="1">
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="15" t="n"/>
+      <c r="S19" s="16" t="n"/>
+      <c r="T19" s="16" t="n"/>
+      <c r="U19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="13.96299999999997" customHeight="1">
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
-      <c r="F20" s="14" t="n"/>
+      <c r="F20" s="17" t="n"/>
       <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
       <c r="J20" s="16" t="n"/>
-      <c r="K20" s="14" t="n"/>
+      <c r="K20" s="17" t="n"/>
       <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
       <c r="O20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="12.928" customHeight="1"/>
-    <row r="22" ht="15.94" customHeight="1">
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="11.84700000000004" customHeight="1"/>
+    <row r="22" ht="14.60699999999997" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>FUNCIONÁRIOS DA SANTELMO</t>
@@ -1461,399 +1361,444 @@
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>EQUIPE DE TERCEIROS</t>
         </is>
       </c>
-      <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="8" t="inlineStr">
         <is>
           <t>EQUIPAMENTOS</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="15.93900000000002" customHeight="1">
-      <c r="B23" s="18" t="inlineStr">
+      <c r="S22" s="4" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="14.608" customHeight="1">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>FUNÇÃO / CARGO</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
       <c r="I23" s="20" t="n"/>
-      <c r="J23" s="18" t="inlineStr">
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="19" t="inlineStr">
         <is>
           <t>QTDE</t>
         </is>
       </c>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="21" t="inlineStr">
+      <c r="L23" s="21" t="n"/>
+      <c r="M23" s="19" t="inlineStr">
         <is>
           <t>EMPRESA / FUNÇÃO</t>
         </is>
       </c>
-      <c r="M23" s="18" t="inlineStr">
+      <c r="N23" s="21" t="n"/>
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>QTDE</t>
         </is>
       </c>
-      <c r="N23" s="19" t="n"/>
-      <c r="O23" s="20" t="n"/>
-      <c r="P23" s="18" t="inlineStr">
+      <c r="P23" s="20" t="n"/>
+      <c r="Q23" s="21" t="n"/>
+      <c r="R23" s="19" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="Q23" s="20" t="n"/>
-      <c r="R23" s="21" t="inlineStr">
+      <c r="S23" s="20" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="22" t="inlineStr">
         <is>
           <t>QTDE</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15.94" customHeight="1">
-      <c r="B24" s="22" t="inlineStr">
+    <row r="24" ht="14.60700000000003" customHeight="1">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>ENG. CIVIL</t>
         </is>
       </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="23" t="n"/>
-      <c r="H24" s="23" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
       <c r="I24" s="24" t="n"/>
-      <c r="J24" s="25" t="n">
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="24" t="n"/>
-      <c r="L24" s="26" t="inlineStr"/>
-      <c r="M24" s="25" t="inlineStr"/>
-      <c r="N24" s="23" t="n"/>
-      <c r="O24" s="24" t="n"/>
-      <c r="P24" s="22" t="inlineStr"/>
-      <c r="Q24" s="24" t="n"/>
-      <c r="R24" s="27" t="inlineStr"/>
-    </row>
-    <row r="25" ht="15.94" customHeight="1">
-      <c r="B25" s="22" t="inlineStr">
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="23" t="inlineStr"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="26" t="inlineStr"/>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="25" t="n"/>
+      <c r="R24" s="23" t="inlineStr"/>
+      <c r="S24" s="24" t="n"/>
+      <c r="T24" s="25" t="n"/>
+      <c r="U24" s="27" t="inlineStr"/>
+    </row>
+    <row r="25" ht="14.608" customHeight="1">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>ENG. ELETRICISTA</t>
         </is>
       </c>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="n"/>
-      <c r="H25" s="23" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
       <c r="I25" s="24" t="n"/>
-      <c r="J25" s="25" t="n">
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="24" t="n"/>
-      <c r="L25" s="26" t="inlineStr"/>
-      <c r="M25" s="25" t="inlineStr"/>
-      <c r="N25" s="23" t="n"/>
-      <c r="O25" s="24" t="n"/>
-      <c r="P25" s="22" t="inlineStr"/>
-      <c r="Q25" s="24" t="n"/>
-      <c r="R25" s="27" t="inlineStr"/>
-    </row>
-    <row r="26" ht="15.94" customHeight="1">
-      <c r="B26" s="22" t="inlineStr">
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="23" t="inlineStr"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="26" t="inlineStr"/>
+      <c r="P25" s="24" t="n"/>
+      <c r="Q25" s="25" t="n"/>
+      <c r="R25" s="23" t="inlineStr"/>
+      <c r="S25" s="24" t="n"/>
+      <c r="T25" s="25" t="n"/>
+      <c r="U25" s="27" t="inlineStr"/>
+    </row>
+    <row r="26" ht="14.60699999999997" customHeight="1">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>ESTAGIÁRIO</t>
         </is>
       </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="23" t="n"/>
-      <c r="H26" s="23" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
       <c r="I26" s="24" t="n"/>
-      <c r="J26" s="25" t="n">
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="24" t="n"/>
-      <c r="L26" s="26" t="inlineStr"/>
-      <c r="M26" s="25" t="inlineStr"/>
-      <c r="N26" s="23" t="n"/>
-      <c r="O26" s="24" t="n"/>
-      <c r="P26" s="22" t="inlineStr"/>
-      <c r="Q26" s="24" t="n"/>
-      <c r="R26" s="27" t="inlineStr"/>
-    </row>
-    <row r="27" ht="15.93899999999996" customHeight="1">
-      <c r="B27" s="22" t="inlineStr">
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="23" t="inlineStr"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="26" t="inlineStr"/>
+      <c r="P26" s="24" t="n"/>
+      <c r="Q26" s="25" t="n"/>
+      <c r="R26" s="23" t="inlineStr"/>
+      <c r="S26" s="24" t="n"/>
+      <c r="T26" s="25" t="n"/>
+      <c r="U26" s="27" t="inlineStr"/>
+    </row>
+    <row r="27" ht="14.608" customHeight="1">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>MESTRE DE OBRAS</t>
         </is>
       </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="23" t="n"/>
-      <c r="H27" s="23" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
       <c r="I27" s="24" t="n"/>
-      <c r="J27" s="25" t="n">
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="24" t="n"/>
-      <c r="L27" s="26" t="inlineStr"/>
-      <c r="M27" s="25" t="inlineStr"/>
-      <c r="N27" s="23" t="n"/>
-      <c r="O27" s="24" t="n"/>
-      <c r="P27" s="22" t="inlineStr"/>
-      <c r="Q27" s="24" t="n"/>
-      <c r="R27" s="27" t="inlineStr"/>
-    </row>
-    <row r="28" ht="15.94000000000005" customHeight="1">
-      <c r="B28" s="22" t="inlineStr">
+      <c r="L27" s="25" t="n"/>
+      <c r="M27" s="23" t="inlineStr"/>
+      <c r="N27" s="25" t="n"/>
+      <c r="O27" s="26" t="inlineStr"/>
+      <c r="P27" s="24" t="n"/>
+      <c r="Q27" s="25" t="n"/>
+      <c r="R27" s="23" t="inlineStr"/>
+      <c r="S27" s="24" t="n"/>
+      <c r="T27" s="25" t="n"/>
+      <c r="U27" s="27" t="inlineStr"/>
+    </row>
+    <row r="28" ht="14.60700000000003" customHeight="1">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>PEDREIRO</t>
         </is>
       </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="23" t="n"/>
-      <c r="H28" s="23" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
       <c r="I28" s="24" t="n"/>
-      <c r="J28" s="25" t="n">
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="24" t="n"/>
-      <c r="L28" s="26" t="inlineStr"/>
-      <c r="M28" s="25" t="inlineStr"/>
-      <c r="N28" s="23" t="n"/>
-      <c r="O28" s="24" t="n"/>
-      <c r="P28" s="22" t="inlineStr"/>
-      <c r="Q28" s="24" t="n"/>
-      <c r="R28" s="27" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15.94" customHeight="1">
-      <c r="B29" s="22" t="inlineStr">
+      <c r="L28" s="25" t="n"/>
+      <c r="M28" s="23" t="inlineStr"/>
+      <c r="N28" s="25" t="n"/>
+      <c r="O28" s="26" t="inlineStr"/>
+      <c r="P28" s="24" t="n"/>
+      <c r="Q28" s="25" t="n"/>
+      <c r="R28" s="23" t="inlineStr"/>
+      <c r="S28" s="24" t="n"/>
+      <c r="T28" s="25" t="n"/>
+      <c r="U28" s="27" t="inlineStr"/>
+    </row>
+    <row r="29" ht="14.608" customHeight="1">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>ELETRICISTA</t>
         </is>
       </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="23" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
       <c r="I29" s="24" t="n"/>
-      <c r="J29" s="25" t="n">
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="24" t="n"/>
-      <c r="L29" s="26" t="inlineStr"/>
-      <c r="M29" s="25" t="inlineStr"/>
-      <c r="N29" s="23" t="n"/>
-      <c r="O29" s="24" t="n"/>
-      <c r="P29" s="22" t="inlineStr"/>
-      <c r="Q29" s="24" t="n"/>
-      <c r="R29" s="27" t="inlineStr"/>
-    </row>
-    <row r="30" ht="15.94" customHeight="1">
-      <c r="B30" s="22" t="inlineStr">
+      <c r="L29" s="25" t="n"/>
+      <c r="M29" s="23" t="inlineStr"/>
+      <c r="N29" s="25" t="n"/>
+      <c r="O29" s="26" t="inlineStr"/>
+      <c r="P29" s="24" t="n"/>
+      <c r="Q29" s="25" t="n"/>
+      <c r="R29" s="23" t="inlineStr"/>
+      <c r="S29" s="24" t="n"/>
+      <c r="T29" s="25" t="n"/>
+      <c r="U29" s="27" t="inlineStr"/>
+    </row>
+    <row r="30" ht="14.60699999999997" customHeight="1">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>SERVENTE</t>
         </is>
       </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
-      <c r="G30" s="23" t="n"/>
-      <c r="H30" s="23" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
       <c r="I30" s="24" t="n"/>
-      <c r="J30" s="25" t="n">
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="24" t="n"/>
-      <c r="L30" s="26" t="inlineStr"/>
-      <c r="M30" s="25" t="inlineStr"/>
-      <c r="N30" s="23" t="n"/>
-      <c r="O30" s="24" t="n"/>
-      <c r="P30" s="22" t="inlineStr"/>
-      <c r="Q30" s="24" t="n"/>
-      <c r="R30" s="27" t="inlineStr"/>
-    </row>
-    <row r="31" ht="15.93899999999996" customHeight="1">
-      <c r="B31" s="22" t="inlineStr">
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="23" t="inlineStr"/>
+      <c r="N30" s="25" t="n"/>
+      <c r="O30" s="26" t="inlineStr"/>
+      <c r="P30" s="24" t="n"/>
+      <c r="Q30" s="25" t="n"/>
+      <c r="R30" s="23" t="inlineStr"/>
+      <c r="S30" s="24" t="n"/>
+      <c r="T30" s="25" t="n"/>
+      <c r="U30" s="27" t="inlineStr"/>
+    </row>
+    <row r="31" ht="14.608" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>CARPINTEIRO</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
-      <c r="G31" s="23" t="n"/>
-      <c r="H31" s="23" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
       <c r="I31" s="24" t="n"/>
-      <c r="J31" s="25" t="n">
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="24" t="n"/>
-      <c r="L31" s="26" t="inlineStr"/>
-      <c r="M31" s="25" t="inlineStr"/>
-      <c r="N31" s="23" t="n"/>
-      <c r="O31" s="24" t="n"/>
-      <c r="P31" s="22" t="inlineStr"/>
-      <c r="Q31" s="24" t="n"/>
-      <c r="R31" s="27" t="inlineStr"/>
-    </row>
-    <row r="32" ht="15.94" customHeight="1">
-      <c r="B32" s="22" t="inlineStr">
+      <c r="L31" s="25" t="n"/>
+      <c r="M31" s="23" t="inlineStr"/>
+      <c r="N31" s="25" t="n"/>
+      <c r="O31" s="26" t="inlineStr"/>
+      <c r="P31" s="24" t="n"/>
+      <c r="Q31" s="25" t="n"/>
+      <c r="R31" s="23" t="inlineStr"/>
+      <c r="S31" s="24" t="n"/>
+      <c r="T31" s="25" t="n"/>
+      <c r="U31" s="27" t="inlineStr"/>
+    </row>
+    <row r="32" ht="14.60699999999997" customHeight="1">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>FERREIRO</t>
         </is>
       </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="23" t="n"/>
-      <c r="G32" s="23" t="n"/>
-      <c r="H32" s="23" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
       <c r="I32" s="24" t="n"/>
-      <c r="J32" s="25" t="n">
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="24" t="n"/>
-      <c r="L32" s="26" t="inlineStr"/>
-      <c r="M32" s="25" t="inlineStr"/>
-      <c r="N32" s="23" t="n"/>
-      <c r="O32" s="24" t="n"/>
-      <c r="P32" s="22" t="inlineStr"/>
-      <c r="Q32" s="24" t="n"/>
-      <c r="R32" s="27" t="inlineStr"/>
-    </row>
-    <row r="33" ht="15.94" customHeight="1">
-      <c r="B33" s="22" t="inlineStr">
+      <c r="L32" s="25" t="n"/>
+      <c r="M32" s="23" t="inlineStr"/>
+      <c r="N32" s="25" t="n"/>
+      <c r="O32" s="26" t="inlineStr"/>
+      <c r="P32" s="24" t="n"/>
+      <c r="Q32" s="25" t="n"/>
+      <c r="R32" s="23" t="inlineStr"/>
+      <c r="S32" s="24" t="n"/>
+      <c r="T32" s="25" t="n"/>
+      <c r="U32" s="27" t="inlineStr"/>
+    </row>
+    <row r="33" ht="14.608" customHeight="1">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>BOMBEIRO HIDRÁULICO</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="23" t="n"/>
-      <c r="H33" s="23" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
       <c r="I33" s="24" t="n"/>
-      <c r="J33" s="25" t="n">
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="24" t="n"/>
-      <c r="L33" s="26" t="inlineStr"/>
-      <c r="M33" s="25" t="inlineStr"/>
-      <c r="N33" s="23" t="n"/>
-      <c r="O33" s="24" t="n"/>
-      <c r="P33" s="22" t="inlineStr"/>
-      <c r="Q33" s="24" t="n"/>
-      <c r="R33" s="27" t="inlineStr"/>
-    </row>
-    <row r="34" ht="15.94000000000005" customHeight="1">
-      <c r="B34" s="22" t="inlineStr">
+      <c r="L33" s="25" t="n"/>
+      <c r="M33" s="23" t="inlineStr"/>
+      <c r="N33" s="25" t="n"/>
+      <c r="O33" s="26" t="inlineStr"/>
+      <c r="P33" s="24" t="n"/>
+      <c r="Q33" s="25" t="n"/>
+      <c r="R33" s="23" t="inlineStr"/>
+      <c r="S33" s="24" t="n"/>
+      <c r="T33" s="25" t="n"/>
+      <c r="U33" s="27" t="inlineStr"/>
+    </row>
+    <row r="34" ht="14.60700000000003" customHeight="1">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>PINTOR</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="23" t="n"/>
-      <c r="H34" s="23" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
       <c r="I34" s="24" t="n"/>
-      <c r="J34" s="25" t="n">
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="24" t="n"/>
-      <c r="L34" s="26" t="inlineStr"/>
-      <c r="M34" s="25" t="inlineStr"/>
-      <c r="N34" s="23" t="n"/>
-      <c r="O34" s="24" t="n"/>
-      <c r="P34" s="22" t="inlineStr"/>
-      <c r="Q34" s="24" t="n"/>
-      <c r="R34" s="27" t="inlineStr"/>
-    </row>
-    <row r="35" ht="15.93899999999996" customHeight="1">
-      <c r="B35" s="22" t="inlineStr"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="23" t="n"/>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="23" t="n"/>
-      <c r="H35" s="23" t="n"/>
+      <c r="L34" s="25" t="n"/>
+      <c r="M34" s="23" t="inlineStr"/>
+      <c r="N34" s="25" t="n"/>
+      <c r="O34" s="26" t="inlineStr"/>
+      <c r="P34" s="24" t="n"/>
+      <c r="Q34" s="25" t="n"/>
+      <c r="R34" s="23" t="inlineStr"/>
+      <c r="S34" s="24" t="n"/>
+      <c r="T34" s="25" t="n"/>
+      <c r="U34" s="27" t="inlineStr"/>
+    </row>
+    <row r="35" ht="14.608" customHeight="1">
+      <c r="B35" s="23" t="inlineStr"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
       <c r="I35" s="24" t="n"/>
-      <c r="J35" s="25" t="inlineStr"/>
-      <c r="K35" s="24" t="n"/>
-      <c r="L35" s="26" t="inlineStr"/>
-      <c r="M35" s="25" t="inlineStr"/>
-      <c r="N35" s="23" t="n"/>
-      <c r="O35" s="24" t="n"/>
-      <c r="P35" s="22" t="inlineStr"/>
-      <c r="Q35" s="24" t="n"/>
-      <c r="R35" s="27" t="inlineStr"/>
-    </row>
-    <row r="36" ht="15.94000000000005" customHeight="1">
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="26" t="inlineStr"/>
+      <c r="L35" s="25" t="n"/>
+      <c r="M35" s="23" t="inlineStr"/>
+      <c r="N35" s="25" t="n"/>
+      <c r="O35" s="26" t="inlineStr"/>
+      <c r="P35" s="24" t="n"/>
+      <c r="Q35" s="25" t="n"/>
+      <c r="R35" s="23" t="inlineStr"/>
+      <c r="S35" s="24" t="n"/>
+      <c r="T35" s="25" t="n"/>
+      <c r="U35" s="27" t="inlineStr"/>
+    </row>
+    <row r="36" ht="14.60699999999997" customHeight="1">
       <c r="B36" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
       <c r="I36" s="24" t="n"/>
-      <c r="J36" s="29" t="n">
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="24" t="n"/>
-      <c r="L36" s="30" t="inlineStr">
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="M36" s="29" t="n">
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="23" t="n"/>
-      <c r="O36" s="24" t="n"/>
-      <c r="P36" s="28" t="inlineStr">
+      <c r="P36" s="24" t="n"/>
+      <c r="Q36" s="25" t="n"/>
+      <c r="R36" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="Q36" s="24" t="n"/>
-      <c r="R36" s="31" t="n">
+      <c r="S36" s="24" t="n"/>
+      <c r="T36" s="25" t="n"/>
+      <c r="U36" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="55.87099999999998" customHeight="1"/>
-    <row r="38" ht="15.93999999999994" customHeight="1">
+    <row r="37" ht="51.202" customHeight="1"/>
+    <row r="38" ht="14.60699999999997" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
           <t>TOTAL DE FUNCIONÁRIOS: 4</t>
@@ -1869,41 +1814,47 @@
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
-      <c r="M38" s="5" t="n"/>
-      <c r="P38" s="8" t="inlineStr">
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="R38" s="8" t="inlineStr">
         <is>
           <t>TOTAL DE EQUIPAMENTOS: 0</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="13.36099999999999" customHeight="1"/>
-    <row r="40" ht="38.67700000000002" customHeight="1">
-      <c r="B40" s="22" t="inlineStr">
+      <c r="S38" s="4" t="n"/>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="12.245" customHeight="1"/>
+    <row r="40" ht="35.44500000000005" customHeight="1">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>OBSERVAÇÕES: DEMONSTRAÇÃO: dados e fotos gerais da semana transcritos do PDF Casa Bosque.</t>
         </is>
       </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="23" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="23" t="n"/>
-      <c r="L40" s="23" t="n"/>
-      <c r="M40" s="23" t="n"/>
-      <c r="N40" s="23" t="n"/>
-      <c r="O40" s="23" t="n"/>
-      <c r="P40" s="23" t="n"/>
-      <c r="Q40" s="23" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="24" t="n"/>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="24" t="n"/>
+      <c r="L40" s="24" t="n"/>
+      <c r="M40" s="24" t="n"/>
+      <c r="N40" s="24" t="n"/>
+      <c r="O40" s="24" t="n"/>
+      <c r="P40" s="24" t="n"/>
+      <c r="Q40" s="24" t="n"/>
       <c r="R40" s="24" t="n"/>
-    </row>
-    <row r="41" ht="7.73599999999999" customHeight="1"/>
-    <row r="42" ht="20.18799999999999" customHeight="1">
+      <c r="S40" s="24" t="n"/>
+      <c r="T40" s="24" t="n"/>
+      <c r="U40" s="25" t="n"/>
+    </row>
+    <row r="41" ht="7.088999999999942" customHeight="1"/>
+    <row r="42" ht="18.50100000000009" customHeight="1">
       <c r="B42" s="3" t="inlineStr">
         <is>
           <t>DIA</t>
@@ -1914,13 +1865,13 @@
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>SERVIÇOS EXECUTADOS</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
@@ -1928,198 +1879,697 @@
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
-      <c r="R42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="60.36000000000001" customHeight="1">
-      <c r="B43" s="32" t="inlineStr">
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="55.31499999999994" customHeight="1">
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C43" s="33" t="n"/>
-      <c r="D43" s="34" t="n"/>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="33" t="n"/>
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
-      <c r="F43" s="36" t="n"/>
-      <c r="G43" s="36" t="n"/>
-      <c r="H43" s="37" t="n"/>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="G43" s="35" t="n"/>
+      <c r="H43" s="35" t="n"/>
+      <c r="I43" s="36" t="n"/>
+      <c r="J43" s="23" t="inlineStr">
         <is>
           <t>ESCAVAÇÃO SAPATAS REMANESCENTES + EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
         </is>
       </c>
-      <c r="J43" s="23" t="n"/>
-      <c r="K43" s="23" t="n"/>
-      <c r="L43" s="23" t="n"/>
-      <c r="M43" s="23" t="n"/>
-      <c r="N43" s="23" t="n"/>
-      <c r="O43" s="23" t="n"/>
-      <c r="P43" s="23" t="n"/>
-      <c r="Q43" s="23" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
+      <c r="M43" s="24" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="24" t="n"/>
+      <c r="P43" s="24" t="n"/>
+      <c r="Q43" s="24" t="n"/>
       <c r="R43" s="24" t="n"/>
-    </row>
-    <row r="44" ht="60.36000000000001" customHeight="1">
-      <c r="B44" s="32" t="inlineStr">
+      <c r="S43" s="24" t="n"/>
+      <c r="T43" s="24" t="n"/>
+      <c r="U43" s="25" t="n"/>
+    </row>
+    <row r="44" ht="55.31500000000005" customHeight="1">
+      <c r="B44" s="31" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C44" s="33" t="n"/>
-      <c r="D44" s="34" t="n"/>
-      <c r="E44" s="35" t="inlineStr">
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="33" t="n"/>
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>TER</t>
         </is>
       </c>
-      <c r="F44" s="36" t="n"/>
-      <c r="G44" s="36" t="n"/>
-      <c r="H44" s="37" t="n"/>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="G44" s="35" t="n"/>
+      <c r="H44" s="35" t="n"/>
+      <c r="I44" s="36" t="n"/>
+      <c r="J44" s="23" t="inlineStr">
         <is>
           <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM ARMADURAS +
 MONTAGEM FÔRMAS PARA CONCRETAGEM VIGAS BALDRAME</t>
         </is>
       </c>
-      <c r="J44" s="23" t="n"/>
-      <c r="K44" s="23" t="n"/>
-      <c r="L44" s="23" t="n"/>
-      <c r="M44" s="23" t="n"/>
-      <c r="N44" s="23" t="n"/>
-      <c r="O44" s="23" t="n"/>
-      <c r="P44" s="23" t="n"/>
-      <c r="Q44" s="23" t="n"/>
+      <c r="K44" s="24" t="n"/>
+      <c r="L44" s="24" t="n"/>
+      <c r="M44" s="24" t="n"/>
+      <c r="N44" s="24" t="n"/>
+      <c r="O44" s="24" t="n"/>
+      <c r="P44" s="24" t="n"/>
+      <c r="Q44" s="24" t="n"/>
       <c r="R44" s="24" t="n"/>
-    </row>
-    <row r="45" ht="19.84299999999996" customHeight="1"/>
+      <c r="S44" s="24" t="n"/>
+      <c r="T44" s="24" t="n"/>
+      <c r="U44" s="25" t="n"/>
+    </row>
+    <row r="45" ht="55.31499999999994" customHeight="1">
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+      <c r="E45" s="33" t="n"/>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>QUA</t>
+        </is>
+      </c>
+      <c r="G45" s="35" t="n"/>
+      <c r="H45" s="35" t="n"/>
+      <c r="I45" s="36" t="n"/>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETAGEM DA VIGA BALDRAME</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="n"/>
+      <c r="L45" s="24" t="n"/>
+      <c r="M45" s="24" t="n"/>
+      <c r="N45" s="24" t="n"/>
+      <c r="O45" s="24" t="n"/>
+      <c r="P45" s="24" t="n"/>
+      <c r="Q45" s="24" t="n"/>
+      <c r="R45" s="24" t="n"/>
+      <c r="S45" s="24" t="n"/>
+      <c r="T45" s="24" t="n"/>
+      <c r="U45" s="25" t="n"/>
+    </row>
+    <row r="46" ht="55.31500000000005" customHeight="1">
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="33" t="n"/>
+      <c r="F46" s="34" t="inlineStr">
+        <is>
+          <t>QUI</t>
+        </is>
+      </c>
+      <c r="G46" s="35" t="n"/>
+      <c r="H46" s="35" t="n"/>
+      <c r="I46" s="36" t="n"/>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETAGEM VIGAS BALDRAME + CONCLUSÃO MONTAGEM FÔRMAS VIGAS BALDRAME +
+MONTAGEM ARMADURAS PILARES TODAS SAPATAS</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="24" t="n"/>
+      <c r="M46" s="24" t="n"/>
+      <c r="N46" s="24" t="n"/>
+      <c r="O46" s="24" t="n"/>
+      <c r="P46" s="24" t="n"/>
+      <c r="Q46" s="24" t="n"/>
+      <c r="R46" s="24" t="n"/>
+      <c r="S46" s="24" t="n"/>
+      <c r="T46" s="24" t="n"/>
+      <c r="U46" s="25" t="n"/>
+    </row>
+    <row r="47" ht="55.31600000000003" customHeight="1">
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="33" t="n"/>
+      <c r="F47" s="34" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="n"/>
+      <c r="H47" s="35" t="n"/>
+      <c r="I47" s="36" t="n"/>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS
+INTERNAS VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="n"/>
+      <c r="L47" s="24" t="n"/>
+      <c r="M47" s="24" t="n"/>
+      <c r="N47" s="24" t="n"/>
+      <c r="O47" s="24" t="n"/>
+      <c r="P47" s="24" t="n"/>
+      <c r="Q47" s="24" t="n"/>
+      <c r="R47" s="24" t="n"/>
+      <c r="S47" s="24" t="n"/>
+      <c r="T47" s="24" t="n"/>
+      <c r="U47" s="25" t="n"/>
+    </row>
+    <row r="48" ht="12.8889999999999" customHeight="1"/>
+    <row r="49" ht="18.50100000000009" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>CHEGADA DE MATERIAIS</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="4" t="n"/>
+      <c r="R49" s="4" t="n"/>
+      <c r="S49" s="4" t="n"/>
+      <c r="T49" s="4" t="n"/>
+      <c r="U49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="19.41800000000001" customHeight="1">
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr"/>
+      <c r="D50" s="24" t="n"/>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="24" t="n"/>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="24" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="24" t="n"/>
+      <c r="L50" s="24" t="n"/>
+      <c r="M50" s="24" t="n"/>
+      <c r="N50" s="24" t="n"/>
+      <c r="O50" s="24" t="n"/>
+      <c r="P50" s="24" t="n"/>
+      <c r="Q50" s="24" t="n"/>
+      <c r="R50" s="24" t="n"/>
+      <c r="S50" s="24" t="n"/>
+      <c r="T50" s="24" t="n"/>
+      <c r="U50" s="25" t="n"/>
+    </row>
+    <row r="51" ht="19.41800000000001" customHeight="1">
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr"/>
+      <c r="D51" s="24" t="n"/>
+      <c r="E51" s="24" t="n"/>
+      <c r="F51" s="24" t="n"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="24" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="24" t="n"/>
+      <c r="L51" s="24" t="n"/>
+      <c r="M51" s="24" t="n"/>
+      <c r="N51" s="24" t="n"/>
+      <c r="O51" s="24" t="n"/>
+      <c r="P51" s="24" t="n"/>
+      <c r="Q51" s="24" t="n"/>
+      <c r="R51" s="24" t="n"/>
+      <c r="S51" s="24" t="n"/>
+      <c r="T51" s="24" t="n"/>
+      <c r="U51" s="25" t="n"/>
+    </row>
+    <row r="52" ht="19.41899999999998" customHeight="1">
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+      <c r="I52" s="24" t="n"/>
+      <c r="J52" s="24" t="n"/>
+      <c r="K52" s="24" t="n"/>
+      <c r="L52" s="24" t="n"/>
+      <c r="M52" s="24" t="n"/>
+      <c r="N52" s="24" t="n"/>
+      <c r="O52" s="24" t="n"/>
+      <c r="P52" s="24" t="n"/>
+      <c r="Q52" s="24" t="n"/>
+      <c r="R52" s="24" t="n"/>
+      <c r="S52" s="24" t="n"/>
+      <c r="T52" s="24" t="n"/>
+      <c r="U52" s="25" t="n"/>
+    </row>
+    <row r="53" ht="19.41799999999989" customHeight="1">
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr"/>
+      <c r="D53" s="24" t="n"/>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
+      <c r="K53" s="24" t="n"/>
+      <c r="L53" s="24" t="n"/>
+      <c r="M53" s="24" t="n"/>
+      <c r="N53" s="24" t="n"/>
+      <c r="O53" s="24" t="n"/>
+      <c r="P53" s="24" t="n"/>
+      <c r="Q53" s="24" t="n"/>
+      <c r="R53" s="24" t="n"/>
+      <c r="S53" s="24" t="n"/>
+      <c r="T53" s="24" t="n"/>
+      <c r="U53" s="25" t="n"/>
+    </row>
+    <row r="54" ht="19.41800000000012" customHeight="1">
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr"/>
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="24" t="n"/>
+      <c r="F54" s="24" t="n"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="24" t="n"/>
+      <c r="J54" s="24" t="n"/>
+      <c r="K54" s="24" t="n"/>
+      <c r="L54" s="24" t="n"/>
+      <c r="M54" s="24" t="n"/>
+      <c r="N54" s="24" t="n"/>
+      <c r="O54" s="24" t="n"/>
+      <c r="P54" s="24" t="n"/>
+      <c r="Q54" s="24" t="n"/>
+      <c r="R54" s="24" t="n"/>
+      <c r="S54" s="24" t="n"/>
+      <c r="T54" s="24" t="n"/>
+      <c r="U54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="8.592999999999847" customHeight="1"/>
+    <row r="56" ht="18.5010000000002" customHeight="1">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>RELATÓRIO FOTOGRÁFICO</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="10.74099999999999" customHeight="1"/>
+    <row r="58" ht="30.07399999999984" customHeight="1">
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
+        </is>
+      </c>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="38" t="n"/>
+      <c r="E58" s="38" t="n"/>
+      <c r="F58" s="38" t="n"/>
+      <c r="G58" s="38" t="n"/>
+      <c r="H58" s="38" t="n"/>
+      <c r="I58" s="38" t="n"/>
+      <c r="J58" s="38" t="n"/>
+      <c r="K58" s="38" t="n"/>
+      <c r="L58" s="38" t="n"/>
+      <c r="M58" s="38" t="n"/>
+      <c r="N58" s="38" t="n"/>
+      <c r="O58" s="38" t="n"/>
+      <c r="P58" s="38" t="n"/>
+      <c r="Q58" s="38" t="n"/>
+      <c r="R58" s="38" t="n"/>
+      <c r="S58" s="38" t="n"/>
+      <c r="T58" s="38" t="n"/>
+      <c r="U58" s="38" t="n"/>
+    </row>
+    <row r="59" ht="200" customHeight="1"/>
+    <row r="60" ht="47.03899999999999" customHeight="1"/>
+    <row r="61" ht="36.51900000000001" customHeight="1">
+      <c r="B61" s="37" t="inlineStr">
+        <is>
+          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS INTERNAS
+VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="n"/>
+      <c r="D61" s="38" t="n"/>
+      <c r="E61" s="38" t="n"/>
+      <c r="F61" s="38" t="n"/>
+      <c r="G61" s="38" t="n"/>
+      <c r="H61" s="38" t="n"/>
+      <c r="I61" s="38" t="n"/>
+      <c r="J61" s="38" t="n"/>
+      <c r="K61" s="38" t="n"/>
+      <c r="L61" s="38" t="n"/>
+      <c r="M61" s="38" t="n"/>
+      <c r="N61" s="38" t="n"/>
+      <c r="O61" s="38" t="n"/>
+      <c r="P61" s="38" t="n"/>
+      <c r="Q61" s="38" t="n"/>
+      <c r="R61" s="38" t="n"/>
+      <c r="S61" s="38" t="n"/>
+      <c r="T61" s="38" t="n"/>
+      <c r="U61" s="38" t="n"/>
+    </row>
+    <row r="62" ht="200" customHeight="1"/>
+    <row r="63" ht="47.03800000000001" customHeight="1"/>
+    <row r="64" ht="36.51900000000001" customHeight="1">
+      <c r="B64" s="37" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM
+VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="C64" s="38" t="n"/>
+      <c r="D64" s="38" t="n"/>
+      <c r="E64" s="38" t="n"/>
+      <c r="F64" s="38" t="n"/>
+      <c r="G64" s="38" t="n"/>
+      <c r="H64" s="38" t="n"/>
+      <c r="I64" s="38" t="n"/>
+      <c r="J64" s="38" t="n"/>
+      <c r="K64" s="38" t="n"/>
+      <c r="L64" s="38" t="n"/>
+      <c r="M64" s="38" t="n"/>
+      <c r="N64" s="38" t="n"/>
+      <c r="O64" s="38" t="n"/>
+      <c r="P64" s="38" t="n"/>
+      <c r="Q64" s="38" t="n"/>
+      <c r="R64" s="38" t="n"/>
+      <c r="S64" s="38" t="n"/>
+      <c r="T64" s="38" t="n"/>
+      <c r="U64" s="38" t="n"/>
+    </row>
+    <row r="65" ht="200" customHeight="1"/>
+    <row r="66" ht="47.03899999999999" customHeight="1"/>
+    <row r="67" ht="36.51900000000001" customHeight="1">
+      <c r="B67" s="37" t="inlineStr">
+        <is>
+          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM
+VIGAS BALDRAME</t>
+        </is>
+      </c>
+      <c r="C67" s="38" t="n"/>
+      <c r="D67" s="38" t="n"/>
+      <c r="E67" s="38" t="n"/>
+      <c r="F67" s="38" t="n"/>
+      <c r="G67" s="38" t="n"/>
+      <c r="H67" s="38" t="n"/>
+      <c r="I67" s="38" t="n"/>
+      <c r="J67" s="38" t="n"/>
+      <c r="K67" s="38" t="n"/>
+      <c r="L67" s="38" t="n"/>
+      <c r="M67" s="38" t="n"/>
+      <c r="N67" s="38" t="n"/>
+      <c r="O67" s="38" t="n"/>
+      <c r="P67" s="38" t="n"/>
+      <c r="Q67" s="38" t="n"/>
+      <c r="R67" s="38" t="n"/>
+      <c r="S67" s="38" t="n"/>
+      <c r="T67" s="38" t="n"/>
+      <c r="U67" s="38" t="n"/>
+    </row>
+    <row r="68" ht="200" customHeight="1"/>
+    <row r="69" ht="62.07600000000002" customHeight="1"/>
+    <row r="70" ht="19.33300000000008" customHeight="1">
+      <c r="B70" s="39" t="inlineStr">
+        <is>
+          <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="13.96299999999974" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
+        <is>
+          <t>ART Nº: CE20261946083</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="13.96300000000019" customHeight="1">
+      <c r="B72" s="40" t="inlineStr">
+        <is>
+          <t>ALVARÁ: 216/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="13.96300000000019" customHeight="1">
+      <c r="B73" s="40" t="inlineStr">
+        <is>
+          <t>EMPRESA: SANTELMO ENGENHARIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8.592999999999847" customHeight="1"/>
+    <row r="75" ht="15.03699999999981" customHeight="1">
+      <c r="B75" s="41" t="inlineStr">
+        <is>
+          <t>santelmoengenharia@gmail.com</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="4" t="n"/>
+      <c r="R75" s="4" t="n"/>
+      <c r="S75" s="4" t="n"/>
+      <c r="T75" s="4" t="n"/>
+      <c r="U75" s="5" t="n"/>
+    </row>
+    <row r="76" ht="19.8420000000001" customHeight="1"/>
   </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="P18:R19"/>
-    <mergeCell ref="B17:E18"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L32"/>
-    <mergeCell ref="F19:J20"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="B8:R8"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="R24"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="L24"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="R26"/>
-    <mergeCell ref="R35"/>
-    <mergeCell ref="L26"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="L34"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="L27"/>
-    <mergeCell ref="L36"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B19:E20"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="R29"/>
-    <mergeCell ref="H12:P12"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="L28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="R31"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="D11:P11"/>
-    <mergeCell ref="L23"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="R32"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="R33"/>
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="D10:P10"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="R28"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B22:K22"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="R25"/>
-    <mergeCell ref="R30"/>
-    <mergeCell ref="C6:N6"/>
-    <mergeCell ref="B40:R40"/>
-    <mergeCell ref="L30"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="I43:R43"/>
-    <mergeCell ref="L29"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="I42:R42"/>
-    <mergeCell ref="F17:J18"/>
-    <mergeCell ref="L31"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="I44:R44"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="B38:M38"/>
-    <mergeCell ref="R23"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="K17:O18"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="K19:O20"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="R34"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="L33"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="R27"/>
-    <mergeCell ref="G13:P13"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="R36"/>
-    <mergeCell ref="C5:N5"/>
-    <mergeCell ref="L35"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L25"/>
-    <mergeCell ref="C4:N4"/>
+  <mergeCells count="153">
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="L15:Q15"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="B19:F20"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="B72:R72"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="D5:P5"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="U35"/>
+    <mergeCell ref="U34"/>
+    <mergeCell ref="B54"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="U27"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="U36"/>
+    <mergeCell ref="J46:U46"/>
+    <mergeCell ref="U30"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="D6:P6"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="G17:K18"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="B49:U49"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B64:U64"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="G19:K20"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="D4:P4"/>
+    <mergeCell ref="C51:U51"/>
+    <mergeCell ref="E10:S10"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="U26"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="N17:Q18"/>
+    <mergeCell ref="E11:S11"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="B67:U67"/>
+    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="B73:R73"/>
+    <mergeCell ref="J42:U42"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="U25"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J44:U44"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="R29:T29"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="B40:U40"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="U28"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="C52:U52"/>
+    <mergeCell ref="B51"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="U29"/>
+    <mergeCell ref="U23"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="B50"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B58:U58"/>
+    <mergeCell ref="U31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="J47:U47"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="J43:U43"/>
+    <mergeCell ref="L17:M18"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="R18:U19"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="U32"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="D2:P2"/>
+    <mergeCell ref="C54:U54"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="C50:U50"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="B17:F18"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="U24"/>
+    <mergeCell ref="U33"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="R22:U22"/>
+    <mergeCell ref="B75:U75"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="J45:U45"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="B71:R71"/>
+    <mergeCell ref="C53:U53"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="B56:U56"/>
+    <mergeCell ref="B70:U70"/>
+    <mergeCell ref="L19:Q20"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="H13:S13"/>
+    <mergeCell ref="R38:U38"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="I12:S12"/>
+    <mergeCell ref="B52"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="B53"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="R34:T34"/>
   </mergeCells>
-  <conditionalFormatting sqref="P18">
+  <conditionalFormatting sqref="R18">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2129,447 +2579,12 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
-    <col width="2.968190476190477" customWidth="1" min="2" max="2"/>
-    <col width="5.202476190476191" customWidth="1" min="3" max="3"/>
-    <col width="12.54190476190476" customWidth="1" min="4" max="4"/>
-    <col width="56.05542857142858" customWidth="1" min="5" max="5"/>
-    <col width="25.4727619047619" customWidth="1" min="6" max="6"/>
-    <col width="3.065333333333348" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.843" customHeight="1"/>
-    <row r="2" ht="51.768" customHeight="1">
-      <c r="B2" s="32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C2" s="34" t="n"/>
-      <c r="D2" s="38" t="inlineStr">
-        <is>
-          <t>QUA</t>
-        </is>
-      </c>
-      <c r="E2" s="22" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETAGEM DA VIGA BALDRAME</t>
-        </is>
-      </c>
-      <c r="F2" s="24" t="n"/>
-    </row>
-    <row r="3" ht="51.76899999999999" customHeight="1">
-      <c r="B3" s="32" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C3" s="34" t="n"/>
-      <c r="D3" s="38" t="inlineStr">
-        <is>
-          <t>QUI</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETAGEM VIGAS BALDRAME + CONCLUSÃO MONTAGEM FÔRMAS VIGAS BALDRAME +
-MONTAGEM ARMADURAS PILARES TODAS SAPATAS</t>
-        </is>
-      </c>
-      <c r="F3" s="24" t="n"/>
-    </row>
-    <row r="4" ht="51.76900000000001" customHeight="1">
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="n"/>
-      <c r="D4" s="38" t="inlineStr">
-        <is>
-          <t>SEX</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS
-INTERNAS VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="n"/>
-    </row>
-    <row r="5" ht="18.87199999999999" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CHEGADA DE MATERIAIS</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="19.80800000000002" customHeight="1">
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="19.80799999999999" customHeight="1">
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="19.80799999999999" customHeight="1">
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="19.80799999999999" customHeight="1">
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="19.80799999999999" customHeight="1">
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="8.765000000000043" customHeight="1"/>
-    <row r="12" ht="18.87299999999999" customHeight="1">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>RELATÓRIO FOTOGRÁFICO</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="10.95599999999996" customHeight="1"/>
-    <row r="14" ht="30.67800000000005" customHeight="1">
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO SAPATAS REMANESCENTES</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-    </row>
-    <row r="15" ht="373.069" customHeight="1"/>
-    <row r="16" ht="19.72199999999998" customHeight="1">
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="14.24299999999994" customHeight="1">
-      <c r="B17" s="42" t="inlineStr">
-        <is>
-          <t>ART Nº: CE20261946083</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="14.24300000000005" customHeight="1">
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>ALVARÁ: 216/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="14.24299999999994" customHeight="1">
-      <c r="B19" s="42" t="inlineStr">
-        <is>
-          <t>EMPRESA: SANTELMO ENGENHARIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8.766000000000076" customHeight="1"/>
-    <row r="21" ht="15.33799999999997" customHeight="1">
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>santelmoengenharia@gmail.com</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="19.84299999999996" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="D4"/>
-    <mergeCell ref="B9"/>
-    <mergeCell ref="D3"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D2"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E3:F3"/>
-  </mergeCells>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
-    <col width="78.91085714285714" customWidth="1" min="2" max="2"/>
-    <col width="25.4727619047619" customWidth="1" min="3" max="3"/>
-    <col width="3.065333333333348" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.843" customHeight="1"/>
-    <row r="2" ht="18.299" customHeight="1">
-      <c r="B2" s="44" t="inlineStr">
-        <is>
-          <t>RELATÓRIO FOTOGRÁFICO</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="11.448" customHeight="1"/>
-    <row r="4" ht="36.122" customHeight="1">
-      <c r="B4" s="45" t="inlineStr">
-        <is>
-          <t>MONTAGEM FÔRMAS CONCRETAGEM PILARES (P1, P2, P3 E P4) + ATERRO E COMPACTAÇÃO ÁREAS INTERNAS
-VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="n"/>
-    </row>
-    <row r="5" ht="244.352" customHeight="1"/>
-    <row r="6" ht="36.12199999999996" customHeight="1">
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM
-VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="n"/>
-    </row>
-    <row r="7" ht="371.842" customHeight="1"/>
-    <row r="8" ht="19.12299999999993" customHeight="1">
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="13.81100000000004" customHeight="1">
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>ART Nº: CE20261946083</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="13.81100000000004" customHeight="1">
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>ALVARÁ: 216/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="13.81200000000001" customHeight="1">
-      <c r="B11" s="47" t="inlineStr">
-        <is>
-          <t>EMPRESA: SANTELMO ENGENHARIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="8.49899999999991" customHeight="1"/>
-    <row r="13" ht="14.87300000000005" customHeight="1">
-      <c r="B13" s="48" t="inlineStr">
-        <is>
-          <t>santelmoengenharia@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="19.84299999999996" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B9"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B4:C4"/>
-  </mergeCells>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.065333333333333" customWidth="1" min="1" max="1"/>
-    <col width="78.91085714285714" customWidth="1" min="2" max="2"/>
-    <col width="25.4727619047619" customWidth="1" min="3" max="3"/>
-    <col width="3.065333333333348" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.843" customHeight="1"/>
-    <row r="2" ht="18.299" customHeight="1">
-      <c r="B2" s="44" t="inlineStr">
-        <is>
-          <t>RELATÓRIO FOTOGRÁFICO</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="11.448" customHeight="1"/>
-    <row r="4" ht="36.122" customHeight="1">
-      <c r="B4" s="45" t="inlineStr">
-        <is>
-          <t>EXEC. CONCRETO MAGRO PARA RECEBIMENTO VIGAS BALDRAME + MONTAGEM FÔRMAS PARA CONCRETAGEM
-VIGAS BALDRAME</t>
-        </is>
-      </c>
-      <c r="C4" s="40" t="n"/>
-    </row>
-    <row r="5" ht="652.316" customHeight="1"/>
-    <row r="6" ht="19.12299999999993" customHeight="1">
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>ENGENHEIRO RESPONSÁVEL: DANILO FONSECA | CREA: 1915794803</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="13.81100000000004" customHeight="1">
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>ART Nº: CE20261946083</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="13.81100000000004" customHeight="1">
-      <c r="B8" s="47" t="inlineStr">
-        <is>
-          <t>ALVARÁ: 216/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="13.81200000000001" customHeight="1">
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>EMPRESA: SANTELMO ENGENHARIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="8.49899999999991" customHeight="1"/>
-    <row r="11" ht="14.87300000000005" customHeight="1">
-      <c r="B11" s="48" t="inlineStr">
-        <is>
-          <t>santelmoengenharia@gmail.com</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="19.84299999999996" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="B4:C4"/>
-  </mergeCells>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
